--- a/output/instructor/tables/instructor_integrated_analysis_results_FINAL.xlsx
+++ b/output/instructor/tables/instructor_integrated_analysis_results_FINAL.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="21600" windowHeight="9555" firstSheet="15" activeTab="19"/>
+    <workbookView windowWidth="21600" windowHeight="9555" firstSheet="4" activeTab="4"/>
   </bookViews>
   <sheets>
     <sheet name="Workbook Guide" sheetId="1" r:id="rId1"/>
@@ -25,8 +25,9 @@
     <sheet name="Phase 4B Fisher" sheetId="16" r:id="rId16"/>
     <sheet name="Phase 4C Models" sheetId="17" r:id="rId17"/>
     <sheet name="Phase 6 Joint Display" sheetId="18" r:id="rId18"/>
-    <sheet name="Method Notes" sheetId="19" r:id="rId19"/>
-    <sheet name="Source Manifest" sheetId="20" r:id="rId20"/>
+    <sheet name="Figures" sheetId="21" r:id="rId19"/>
+    <sheet name="Method Notes" sheetId="19" r:id="rId20"/>
+    <sheet name="Source Manifest" sheetId="20" r:id="rId21"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Workbook Guide'!$A$4:$B$10</definedName>
@@ -46,9 +47,9 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="14" hidden="1">'Phase 4B Associations'!$A$4:$H$11</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="15" hidden="1">'Phase 4B Fisher'!$A$4:$M$8</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="16" hidden="1">'Phase 4C Models'!$A$4:$N$9</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="17" hidden="1">'Phase 6 Joint Display'!$A$4:$F$11</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="18" hidden="1">'Method Notes'!$A$4:$C$12</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="19" hidden="1">'Source Manifest'!$A$4:$D$9</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="17" hidden="1">'Phase 6 Joint Display'!$A$4:$D$11</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="19" hidden="1">'Method Notes'!$A$4:$C$12</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="20" hidden="1">'Source Manifest'!$A$4:$D$9</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -68,7 +69,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="695" uniqueCount="447">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="678" uniqueCount="440">
   <si>
     <t>Instructor Survey Integrated Analysis Workbook</t>
   </si>
@@ -682,7 +683,27 @@
     <t>q11</t>
   </si>
   <si>
-    <t>9.	Describe what worked well, or did not work well, about the AI-assisted grading workflow from your perspective.</t>
+    <r>
+      <t>9.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">	</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
+      <t>Describe what worked well, or did not work well, about the AI-assisted grading workflow from your perspective.</t>
+    </r>
   </si>
   <si>
     <t>q13</t>
@@ -1195,39 +1216,24 @@
     <t>Phase 6: Joint Display</t>
   </si>
   <si>
-    <t>Quantitative evidence is populated; qualitative evidence remains pending Phase 5 coding.</t>
-  </si>
-  <si>
     <t>quantitative_evidence</t>
   </si>
   <si>
-    <t>qualitative_evidence</t>
-  </si>
-  <si>
     <t>integrated_interpretation</t>
   </si>
   <si>
     <t>design_or_policy_recommendation</t>
   </si>
   <si>
-    <t>strength_of_evidence</t>
-  </si>
-  <si>
     <t>74.2% reported time savings. rho = 0.630; BH-adjusted p = .001; continuation model: OR = 11.66, 95% CI [1.93, 70.61]; BH-adjusted p = .013.</t>
   </si>
   <si>
-    <t>To be completed from Phase 5 open-ended coding.</t>
-  </si>
-  <si>
     <t>Provisional quantitative interpretation: Efficiency appears central to acceptance of the implementation model.</t>
   </si>
   <si>
     <t>Preserve efficiency gains while identifying tasks that add review time.</t>
   </si>
   <si>
-    <t>Descriptive and small-sample analytic evidence</t>
-  </si>
-  <si>
     <t>51.6% reported positive workflow fit. rho = 0.547; BH-adjusted p = .003; continuation model: OR = 2.40, 95% CI [0.88, 6.53]; BH-adjusted p = .086.</t>
   </si>
   <si>
@@ -1273,9 +1279,6 @@
     <t>Retain an explicit and visible human oversight role.</t>
   </si>
   <si>
-    <t>Descriptive evidence; small sample</t>
-  </si>
-  <si>
     <t>No direct quantitative scale was available for this domain. No quantitative inferential result was available.</t>
   </si>
   <si>
@@ -1283,9 +1286,6 @@
   </si>
   <si>
     <t>Complete after Phase 5 qualitative coding.</t>
-  </si>
-  <si>
-    <t>Not assessed quantitatively</t>
   </si>
   <si>
     <t>Methodological and Interpretation Notes</t>
@@ -1424,7 +1424,7 @@
     <numFmt numFmtId="177" formatCode="[&lt;0.001]&quot;&lt; .001&quot;;0.000"/>
     <numFmt numFmtId="178" formatCode="0.0"/>
   </numFmts>
-  <fonts count="25">
+  <fonts count="29">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -1450,6 +1450,26 @@
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
+      <name val="Times New Roman"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
+      <name val="Times New Roman"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
+      <name val="Times New Roman"/>
       <charset val="134"/>
     </font>
     <font>
@@ -1609,6 +1629,12 @@
       <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <charset val="134"/>
     </font>
   </fonts>
   <fills count="33">
@@ -1923,31 +1949,19 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="44" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="9" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="41" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="42" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="42" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1956,119 +1970,131 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -2078,12 +2104,61 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="178" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="178" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="1" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="176" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="2" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="177" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="178" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="49">
@@ -2358,6 +2433,315 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>5080</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>5080</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>81280</xdr:colOff>
+      <xdr:row>30</xdr:row>
+      <xdr:rowOff>62230</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="图片 1" descr="instructor_ai_evaluation_direction"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="5080" y="5080"/>
+          <a:ext cx="9144000" cy="5486400"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>5080</xdr:colOff>
+      <xdr:row>32</xdr:row>
+      <xdr:rowOff>5080</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>81280</xdr:colOff>
+      <xdr:row>59</xdr:row>
+      <xdr:rowOff>147955</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="图片 2" descr="instructor_continuation_recommendation"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="5080" y="5796280"/>
+          <a:ext cx="9144000" cy="5029200"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>5080</xdr:colOff>
+      <xdr:row>62</xdr:row>
+      <xdr:rowOff>5080</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>462280</xdr:colOff>
+      <xdr:row>89</xdr:row>
+      <xdr:rowOff>147955</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="4" name="图片 3" descr="instructor_preferred_model"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="5080" y="11225530"/>
+          <a:ext cx="8229600" cy="5029200"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>5080</xdr:colOff>
+      <xdr:row>92</xdr:row>
+      <xdr:rowOff>5080</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>347980</xdr:colOff>
+      <xdr:row>124</xdr:row>
+      <xdr:rowOff>157480</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="5" name="图片 4" descr="instructor_preferred_model_by_appropriateness"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId4"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="5080" y="16654780"/>
+          <a:ext cx="10058400" cy="5943600"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>5080</xdr:colOff>
+      <xdr:row>127</xdr:row>
+      <xdr:rowOff>5080</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>347980</xdr:colOff>
+      <xdr:row>159</xdr:row>
+      <xdr:rowOff>157480</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="6" name="图片 5" descr="instructor_preferred_model_by_continuation"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId5"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="5080" y="22988905"/>
+          <a:ext cx="10058400" cy="5943600"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>5080</xdr:colOff>
+      <xdr:row>161</xdr:row>
+      <xdr:rowOff>5080</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>462280</xdr:colOff>
+      <xdr:row>188</xdr:row>
+      <xdr:rowOff>147955</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="7" name="图片 6" descr="instructor_review_time"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId6"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="5080" y="29142055"/>
+          <a:ext cx="8229600" cy="5029200"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>5080</xdr:colOff>
+      <xdr:row>191</xdr:row>
+      <xdr:rowOff>5080</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>462280</xdr:colOff>
+      <xdr:row>218</xdr:row>
+      <xdr:rowOff>147955</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="8" name="图片 7" descr="instructor_score_accuracy"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId7"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="5080" y="34571305"/>
+          <a:ext cx="8229600" cy="5029200"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>5080</xdr:colOff>
+      <xdr:row>220</xdr:row>
+      <xdr:rowOff>5080</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>462280</xdr:colOff>
+      <xdr:row>247</xdr:row>
+      <xdr:rowOff>147955</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="9" name="图片 8" descr="instructor_time_impact"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId8"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="5080" y="39819580"/>
+          <a:ext cx="8229600" cy="5029200"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2651,7 +3035,7 @@
       </c>
     </row>
     <row r="2" ht="26.25" spans="1:1">
-      <c r="A2" s="4" t="s">
+      <c r="A2" s="24" t="s">
         <v>1</v>
       </c>
     </row>
@@ -2725,51 +3109,52 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:E5"/>
-  <sheetFormatPr defaultColWidth="11" defaultRowHeight="14.25" outlineLevelRow="4" outlineLevelCol="4"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.35" outlineLevelRow="4" outlineLevelCol="4"/>
   <cols>
-    <col min="1" max="1" width="39.0265486725664" customWidth="1"/>
-    <col min="2" max="2" width="20.5309734513274" customWidth="1"/>
-    <col min="3" max="3" width="12.6017699115044" customWidth="1"/>
-    <col min="4" max="4" width="24.4955752212389" customWidth="1"/>
-    <col min="5" max="5" width="39.0265486725664" customWidth="1"/>
+    <col min="1" max="1" width="39.0265486725664" style="13" customWidth="1"/>
+    <col min="2" max="2" width="20.5309734513274" style="13" customWidth="1"/>
+    <col min="3" max="3" width="12.6017699115044" style="13" customWidth="1"/>
+    <col min="4" max="4" width="24.4955752212389" style="13" customWidth="1"/>
+    <col min="5" max="5" width="39.0265486725664" style="13" customWidth="1"/>
+    <col min="6" max="16384" width="11" style="13"/>
   </cols>
   <sheetData>
-    <row r="1" ht="18" spans="1:1">
-      <c r="A1" s="1" t="s">
+    <row r="1" ht="15" spans="1:1">
+      <c r="A1" s="19" t="s">
         <v>295</v>
       </c>
     </row>
-    <row r="4" spans="1:5">
-      <c r="A4" s="2" t="s">
+    <row r="4" ht="15" spans="1:5">
+      <c r="A4" s="7" t="s">
         <v>127</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="B4" s="7" t="s">
         <v>296</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="C4" s="7" t="s">
         <v>297</v>
       </c>
-      <c r="D4" s="2" t="s">
+      <c r="D4" s="7" t="s">
         <v>298</v>
       </c>
-      <c r="E4" s="2" t="s">
+      <c r="E4" s="7" t="s">
         <v>299</v>
       </c>
     </row>
     <row r="5" spans="1:5">
-      <c r="A5" s="5">
-        <v>31</v>
-      </c>
-      <c r="B5" s="5">
+      <c r="A5" s="15">
+        <v>31</v>
+      </c>
+      <c r="B5" s="15">
         <v>4</v>
       </c>
-      <c r="C5" s="6">
+      <c r="C5" s="16">
         <v>0.649379223636649</v>
       </c>
-      <c r="D5" s="6">
+      <c r="D5" s="16">
         <v>0.649489487873113</v>
       </c>
-      <c r="E5" s="6">
+      <c r="E5" s="16">
         <v>0.316587620689932</v>
       </c>
     </row>
@@ -2787,193 +3172,194 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:K8"/>
-  <sheetFormatPr defaultColWidth="11" defaultRowHeight="14.25" outlineLevelRow="7"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.35" outlineLevelRow="7"/>
   <cols>
-    <col min="1" max="1" width="35.7079646017699" customWidth="1"/>
-    <col min="2" max="2" width="3.70796460176991" customWidth="1"/>
-    <col min="3" max="8" width="11.7079646017699" customWidth="1"/>
-    <col min="9" max="9" width="20.7079646017699" customWidth="1"/>
-    <col min="10" max="10" width="29.7079646017699" customWidth="1"/>
-    <col min="11" max="11" width="20.7079646017699" customWidth="1"/>
+    <col min="1" max="1" width="35.7079646017699" style="13" customWidth="1"/>
+    <col min="2" max="2" width="3.70796460176991" style="13" customWidth="1"/>
+    <col min="3" max="8" width="11.7079646017699" style="13" customWidth="1"/>
+    <col min="9" max="9" width="20.7079646017699" style="13" customWidth="1"/>
+    <col min="10" max="10" width="29.7079646017699" style="13" customWidth="1"/>
+    <col min="11" max="11" width="20.7079646017699" style="13" customWidth="1"/>
+    <col min="12" max="16384" width="11" style="13"/>
   </cols>
   <sheetData>
-    <row r="1" ht="18" spans="1:1">
-      <c r="A1" s="1" t="s">
+    <row r="1" ht="15" spans="1:1">
+      <c r="A1" s="19" t="s">
         <v>300</v>
       </c>
     </row>
-    <row r="4" spans="1:11">
-      <c r="A4" s="2" t="s">
+    <row r="4" ht="15" spans="1:11">
+      <c r="A4" s="7" t="s">
         <v>301</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="B4" s="7" t="s">
         <v>87</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="C4" s="7" t="s">
         <v>302</v>
       </c>
-      <c r="D4" s="2" t="s">
+      <c r="D4" s="7" t="s">
         <v>303</v>
       </c>
-      <c r="E4" s="2" t="s">
+      <c r="E4" s="7" t="s">
         <v>304</v>
       </c>
-      <c r="F4" s="2" t="s">
+      <c r="F4" s="7" t="s">
         <v>305</v>
       </c>
-      <c r="G4" s="2" t="s">
+      <c r="G4" s="7" t="s">
         <v>306</v>
       </c>
-      <c r="H4" s="2" t="s">
+      <c r="H4" s="7" t="s">
         <v>307</v>
       </c>
-      <c r="I4" s="2" t="s">
+      <c r="I4" s="7" t="s">
         <v>308</v>
       </c>
-      <c r="J4" s="2" t="s">
+      <c r="J4" s="7" t="s">
         <v>309</v>
       </c>
-      <c r="K4" s="2" t="s">
+      <c r="K4" s="7" t="s">
         <v>310</v>
       </c>
     </row>
-    <row r="5" spans="1:11">
-      <c r="A5" s="3" t="s">
+    <row r="5" ht="15.4" spans="1:11">
+      <c r="A5" s="14" t="s">
         <v>311</v>
       </c>
-      <c r="B5" s="5">
-        <v>31</v>
-      </c>
-      <c r="C5" s="6">
+      <c r="B5" s="15">
+        <v>31</v>
+      </c>
+      <c r="C5" s="16">
         <v>0.596897511676515</v>
       </c>
-      <c r="D5" s="6">
+      <c r="D5" s="16">
         <v>0.595011577812203</v>
       </c>
-      <c r="E5" s="6">
+      <c r="E5" s="16">
         <v>0.360383184951243</v>
       </c>
-      <c r="F5" s="6">
+      <c r="F5" s="16">
         <v>0.290336147677117</v>
       </c>
-      <c r="G5" s="6">
+      <c r="G5" s="16">
         <v>3.64516129032258</v>
       </c>
-      <c r="H5" s="6">
+      <c r="H5" s="16">
         <v>0.754912228751316</v>
       </c>
-      <c r="I5" s="6">
+      <c r="I5" s="16">
         <v>0.672032193158954</v>
       </c>
-      <c r="J5" s="6">
+      <c r="J5" s="16">
         <v>0.678187224889908</v>
       </c>
-      <c r="K5" s="6">
+      <c r="K5" s="16">
         <v>0.412616623536338</v>
       </c>
     </row>
-    <row r="6" spans="1:11">
-      <c r="A6" s="3" t="s">
+    <row r="6" ht="15.4" spans="1:11">
+      <c r="A6" s="14" t="s">
         <v>312</v>
       </c>
-      <c r="B6" s="5">
-        <v>31</v>
-      </c>
-      <c r="C6" s="6">
+      <c r="B6" s="15">
+        <v>31</v>
+      </c>
+      <c r="C6" s="16">
         <v>0.729250647569977</v>
       </c>
-      <c r="D6" s="6">
+      <c r="D6" s="16">
         <v>0.714979271911082</v>
       </c>
-      <c r="E6" s="6">
+      <c r="E6" s="16">
         <v>0.547813270159413</v>
       </c>
-      <c r="F6" s="6">
+      <c r="F6" s="16">
         <v>0.454794832536857</v>
       </c>
-      <c r="G6" s="6">
+      <c r="G6" s="16">
         <v>3.48387096774194</v>
       </c>
-      <c r="H6" s="6">
+      <c r="H6" s="16">
         <v>0.811211757883866</v>
       </c>
-      <c r="I6" s="6">
+      <c r="I6" s="16">
         <v>0.563099041533546</v>
       </c>
-      <c r="J6" s="6">
+      <c r="J6" s="16">
         <v>0.563599766305292</v>
       </c>
-      <c r="K6" s="6">
+      <c r="K6" s="16">
         <v>0.300939569441116</v>
       </c>
     </row>
-    <row r="7" spans="1:11">
-      <c r="A7" s="3" t="s">
+    <row r="7" ht="15.4" spans="1:11">
+      <c r="A7" s="14" t="s">
         <v>313</v>
       </c>
-      <c r="B7" s="5">
-        <v>31</v>
-      </c>
-      <c r="C7" s="6">
+      <c r="B7" s="15">
+        <v>31</v>
+      </c>
+      <c r="C7" s="16">
         <v>0.762714370465823</v>
       </c>
-      <c r="D7" s="6">
+      <c r="D7" s="16">
         <v>0.763969166327122</v>
       </c>
-      <c r="E7" s="6">
+      <c r="E7" s="16">
         <v>0.683710474757743</v>
       </c>
-      <c r="F7" s="6">
+      <c r="F7" s="16">
         <v>0.52233409033582</v>
       </c>
-      <c r="G7" s="6">
+      <c r="G7" s="16">
         <v>2.70967741935484</v>
       </c>
-      <c r="H7" s="6">
+      <c r="H7" s="16">
         <v>0.782881361258813</v>
       </c>
-      <c r="I7" s="6">
+      <c r="I7" s="16">
         <v>0.512704918032787</v>
       </c>
-      <c r="J7" s="6">
+      <c r="J7" s="16">
         <v>0.507063397449176</v>
       </c>
-      <c r="K7" s="6">
+      <c r="K7" s="16">
         <v>0.255335232957746</v>
       </c>
     </row>
-    <row r="8" spans="1:11">
-      <c r="A8" s="3" t="s">
+    <row r="8" ht="15.4" spans="1:11">
+      <c r="A8" s="14" t="s">
         <v>314</v>
       </c>
-      <c r="B8" s="5">
-        <v>31</v>
-      </c>
-      <c r="C8" s="6">
+      <c r="B8" s="15">
+        <v>31</v>
+      </c>
+      <c r="C8" s="16">
         <v>0.702801358932856</v>
       </c>
-      <c r="D8" s="6">
+      <c r="D8" s="16">
         <v>0.718718169541192</v>
       </c>
-      <c r="E8" s="6">
+      <c r="E8" s="16">
         <v>0.619935448729982</v>
       </c>
-      <c r="F8" s="6">
+      <c r="F8" s="16">
         <v>0.463460000333675</v>
       </c>
-      <c r="G8" s="6">
+      <c r="G8" s="16">
         <v>3.96774193548387</v>
       </c>
-      <c r="H8" s="6">
+      <c r="H8" s="16">
         <v>0.706346042094663</v>
       </c>
-      <c r="I8" s="6">
+      <c r="I8" s="16">
         <v>0.560716898317484</v>
       </c>
-      <c r="J8" s="6">
+      <c r="J8" s="16">
         <v>0.559512844475688</v>
       </c>
-      <c r="K8" s="6">
+      <c r="K8" s="16">
         <v>0.297459056824527</v>
       </c>
     </row>
@@ -2991,101 +3377,102 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:E8"/>
-  <sheetFormatPr defaultColWidth="11" defaultRowHeight="14.25" outlineLevelRow="7" outlineLevelCol="4"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.35" outlineLevelRow="7" outlineLevelCol="4"/>
   <cols>
-    <col min="1" max="1" width="35.7079646017699" customWidth="1"/>
-    <col min="2" max="3" width="22.7079646017699" customWidth="1"/>
-    <col min="4" max="4" width="20.7079646017699" customWidth="1"/>
-    <col min="5" max="5" width="17.7079646017699" customWidth="1"/>
+    <col min="1" max="1" width="35.7079646017699" style="13" customWidth="1"/>
+    <col min="2" max="3" width="22.7079646017699" style="13" customWidth="1"/>
+    <col min="4" max="4" width="20.7079646017699" style="13" customWidth="1"/>
+    <col min="5" max="5" width="17.7079646017699" style="13" customWidth="1"/>
+    <col min="6" max="16384" width="11" style="13"/>
   </cols>
   <sheetData>
-    <row r="1" ht="18" spans="1:1">
-      <c r="A1" s="1" t="s">
+    <row r="1" ht="15" spans="1:1">
+      <c r="A1" s="19" t="s">
         <v>315</v>
       </c>
     </row>
-    <row r="4" spans="1:5">
-      <c r="A4" s="2" t="s">
+    <row r="4" ht="15" spans="1:5">
+      <c r="A4" s="7" t="s">
         <v>301</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="B4" s="7" t="s">
         <v>311</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="C4" s="7" t="s">
         <v>312</v>
       </c>
-      <c r="D4" s="2" t="s">
+      <c r="D4" s="7" t="s">
         <v>313</v>
       </c>
-      <c r="E4" s="2" t="s">
+      <c r="E4" s="7" t="s">
         <v>314</v>
       </c>
     </row>
-    <row r="5" spans="1:5">
-      <c r="A5" s="3" t="s">
+    <row r="5" ht="15.4" spans="1:5">
+      <c r="A5" s="14" t="s">
         <v>311</v>
       </c>
-      <c r="B5" s="6">
+      <c r="B5" s="16">
         <v>1</v>
       </c>
-      <c r="C5" s="6">
+      <c r="C5" s="16">
         <v>0.556872142609627</v>
       </c>
-      <c r="D5" s="6">
+      <c r="D5" s="16">
         <v>0.283581549694993</v>
       </c>
-      <c r="E5" s="6">
+      <c r="E5" s="16">
         <v>0.145350685727202</v>
       </c>
     </row>
-    <row r="6" spans="1:5">
-      <c r="A6" s="3" t="s">
+    <row r="6" ht="15.4" spans="1:5">
+      <c r="A6" s="14" t="s">
         <v>312</v>
       </c>
-      <c r="B6" s="6">
+      <c r="B6" s="16">
         <v>0.556872142609627</v>
       </c>
-      <c r="C6" s="6">
+      <c r="C6" s="16">
         <v>1</v>
       </c>
-      <c r="D6" s="6">
+      <c r="D6" s="16">
         <v>0.418432071195338</v>
       </c>
-      <c r="E6" s="6">
+      <c r="E6" s="16">
         <v>0.407587540967192</v>
       </c>
     </row>
-    <row r="7" spans="1:5">
-      <c r="A7" s="3" t="s">
+    <row r="7" ht="15.4" spans="1:5">
+      <c r="A7" s="14" t="s">
         <v>313</v>
       </c>
-      <c r="B7" s="6">
+      <c r="B7" s="16">
         <v>0.283581549694993</v>
       </c>
-      <c r="C7" s="6">
+      <c r="C7" s="16">
         <v>0.418432071195338</v>
       </c>
-      <c r="D7" s="6">
+      <c r="D7" s="16">
         <v>1</v>
       </c>
-      <c r="E7" s="6">
+      <c r="E7" s="16">
         <v>0.543720632781667</v>
       </c>
     </row>
-    <row r="8" spans="1:5">
-      <c r="A8" s="3" t="s">
+    <row r="8" ht="15.4" spans="1:5">
+      <c r="A8" s="14" t="s">
         <v>314</v>
       </c>
-      <c r="B8" s="6">
+      <c r="B8" s="16">
         <v>0.145350685727202</v>
       </c>
-      <c r="C8" s="6">
+      <c r="C8" s="16">
         <v>0.407587540967192</v>
       </c>
-      <c r="D8" s="6">
+      <c r="D8" s="16">
         <v>0.543720632781667</v>
       </c>
-      <c r="E8" s="6">
+      <c r="E8" s="16">
         <v>1</v>
       </c>
     </row>
@@ -3103,177 +3490,178 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:G10"/>
-  <sheetFormatPr defaultColWidth="11" defaultRowHeight="14.25" outlineLevelCol="6"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.35" outlineLevelCol="6"/>
   <cols>
-    <col min="1" max="2" width="35.7079646017699" customWidth="1"/>
-    <col min="3" max="3" width="10.7079646017699" customWidth="1"/>
-    <col min="4" max="4" width="12.7079646017699" customWidth="1"/>
-    <col min="5" max="7" width="11.7079646017699" customWidth="1"/>
+    <col min="1" max="2" width="35.7079646017699" style="13" customWidth="1"/>
+    <col min="3" max="3" width="10.7079646017699" style="13" customWidth="1"/>
+    <col min="4" max="4" width="17.7256637168142" style="13" customWidth="1"/>
+    <col min="5" max="7" width="11.7079646017699" style="13" customWidth="1"/>
+    <col min="8" max="16384" width="11" style="13"/>
   </cols>
   <sheetData>
-    <row r="1" ht="18" spans="1:1">
-      <c r="A1" s="1" t="s">
+    <row r="1" ht="15" spans="1:1">
+      <c r="A1" s="19" t="s">
         <v>316</v>
       </c>
     </row>
-    <row r="4" spans="1:7">
-      <c r="A4" s="2" t="s">
+    <row r="4" ht="30" spans="1:7">
+      <c r="A4" s="7" t="s">
         <v>317</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="B4" s="7" t="s">
         <v>318</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="C4" s="7" t="s">
         <v>127</v>
       </c>
-      <c r="D4" s="2" t="s">
+      <c r="D4" s="7" t="s">
         <v>319</v>
       </c>
-      <c r="E4" s="2" t="s">
+      <c r="E4" s="7" t="s">
         <v>320</v>
       </c>
-      <c r="F4" s="2" t="s">
+      <c r="F4" s="7" t="s">
         <v>321</v>
       </c>
-      <c r="G4" s="2" t="s">
+      <c r="G4" s="7" t="s">
         <v>322</v>
       </c>
     </row>
-    <row r="5" spans="1:7">
-      <c r="A5" s="3" t="s">
+    <row r="5" ht="15.4" spans="1:7">
+      <c r="A5" s="14" t="s">
         <v>311</v>
       </c>
-      <c r="B5" s="3" t="s">
+      <c r="B5" s="14" t="s">
         <v>312</v>
       </c>
-      <c r="C5" s="5">
-        <v>31</v>
-      </c>
-      <c r="D5" s="6">
+      <c r="C5" s="15">
+        <v>31</v>
+      </c>
+      <c r="D5" s="16">
         <v>0.556872142609627</v>
       </c>
-      <c r="E5" s="6">
+      <c r="E5" s="16">
         <v>2197.91417265625</v>
       </c>
-      <c r="F5" s="8">
+      <c r="F5" s="18">
         <v>0.00113881165106555</v>
       </c>
-      <c r="G5" s="8">
+      <c r="G5" s="18">
         <v>0.00471000953238422</v>
       </c>
     </row>
-    <row r="6" spans="1:7">
-      <c r="A6" s="3" t="s">
+    <row r="6" ht="15.4" spans="1:7">
+      <c r="A6" s="14" t="s">
         <v>313</v>
       </c>
-      <c r="B6" s="3" t="s">
+      <c r="B6" s="14" t="s">
         <v>314</v>
       </c>
-      <c r="C6" s="5">
-        <v>31</v>
-      </c>
-      <c r="D6" s="6">
+      <c r="C6" s="15">
+        <v>31</v>
+      </c>
+      <c r="D6" s="16">
         <v>0.543720632781667</v>
       </c>
-      <c r="E6" s="6">
+      <c r="E6" s="16">
         <v>2263.14566140293</v>
       </c>
-      <c r="F6" s="8">
+      <c r="F6" s="18">
         <v>0.00157000317746141</v>
       </c>
-      <c r="G6" s="8">
+      <c r="G6" s="18">
         <v>0.00471000953238422</v>
       </c>
     </row>
-    <row r="7" spans="1:7">
-      <c r="A7" s="3" t="s">
+    <row r="7" ht="15.4" spans="1:7">
+      <c r="A7" s="14" t="s">
         <v>312</v>
       </c>
-      <c r="B7" s="3" t="s">
+      <c r="B7" s="14" t="s">
         <v>313</v>
       </c>
-      <c r="C7" s="5">
-        <v>31</v>
-      </c>
-      <c r="D7" s="6">
+      <c r="C7" s="15">
+        <v>31</v>
+      </c>
+      <c r="D7" s="16">
         <v>0.418432071195338</v>
       </c>
-      <c r="E7" s="6">
+      <c r="E7" s="16">
         <v>2884.57692687112</v>
       </c>
-      <c r="F7" s="8">
+      <c r="F7" s="18">
         <v>0.0191481514591788</v>
       </c>
-      <c r="G7" s="8">
+      <c r="G7" s="18">
         <v>0.0342743744183243</v>
       </c>
     </row>
-    <row r="8" spans="1:7">
-      <c r="A8" s="3" t="s">
+    <row r="8" ht="15.4" spans="1:7">
+      <c r="A8" s="14" t="s">
         <v>312</v>
       </c>
-      <c r="B8" s="3" t="s">
+      <c r="B8" s="14" t="s">
         <v>314</v>
       </c>
-      <c r="C8" s="5">
-        <v>31</v>
-      </c>
-      <c r="D8" s="6">
+      <c r="C8" s="15">
+        <v>31</v>
+      </c>
+      <c r="D8" s="16">
         <v>0.407587540967192</v>
       </c>
-      <c r="E8" s="6">
+      <c r="E8" s="16">
         <v>2938.36579680273</v>
       </c>
-      <c r="F8" s="8">
+      <c r="F8" s="18">
         <v>0.0228495829455495</v>
       </c>
-      <c r="G8" s="8">
+      <c r="G8" s="18">
         <v>0.0342743744183243</v>
       </c>
     </row>
-    <row r="9" spans="1:7">
-      <c r="A9" s="3" t="s">
+    <row r="9" ht="15.4" spans="1:7">
+      <c r="A9" s="14" t="s">
         <v>311</v>
       </c>
-      <c r="B9" s="3" t="s">
+      <c r="B9" s="14" t="s">
         <v>313</v>
       </c>
-      <c r="C9" s="5">
-        <v>31</v>
-      </c>
-      <c r="D9" s="6">
+      <c r="C9" s="15">
+        <v>31</v>
+      </c>
+      <c r="D9" s="16">
         <v>0.283581549694993</v>
       </c>
-      <c r="E9" s="6">
+      <c r="E9" s="16">
         <v>3553.43551351283</v>
       </c>
-      <c r="F9" s="8">
+      <c r="F9" s="18">
         <v>0.122113383013156</v>
       </c>
-      <c r="G9" s="8">
+      <c r="G9" s="18">
         <v>0.146536059615787</v>
       </c>
     </row>
-    <row r="10" spans="1:7">
-      <c r="A10" s="3" t="s">
+    <row r="10" ht="15.4" spans="1:7">
+      <c r="A10" s="14" t="s">
         <v>311</v>
       </c>
-      <c r="B10" s="3" t="s">
+      <c r="B10" s="14" t="s">
         <v>314</v>
       </c>
-      <c r="C10" s="5">
-        <v>31</v>
-      </c>
-      <c r="D10" s="6">
+      <c r="C10" s="15">
+        <v>31</v>
+      </c>
+      <c r="D10" s="16">
         <v>0.145350685727202</v>
       </c>
-      <c r="E10" s="6">
+      <c r="E10" s="16">
         <v>4239.06059879308</v>
       </c>
-      <c r="F10" s="8">
+      <c r="F10" s="18">
         <v>0.435285847092907</v>
       </c>
-      <c r="G10" s="8">
+      <c r="G10" s="18">
         <v>0.435285847092907</v>
       </c>
     </row>
@@ -3291,106 +3679,107 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:E8"/>
-  <sheetFormatPr defaultColWidth="11" defaultRowHeight="14.25" outlineLevelRow="7" outlineLevelCol="4"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.35" outlineLevelRow="7" outlineLevelCol="4"/>
   <cols>
-    <col min="1" max="1" width="35.7079646017699" customWidth="1"/>
-    <col min="2" max="3" width="22.7079646017699" customWidth="1"/>
-    <col min="4" max="4" width="20.7079646017699" customWidth="1"/>
-    <col min="5" max="5" width="17.7079646017699" customWidth="1"/>
+    <col min="1" max="1" width="45.2743362831858" style="13" customWidth="1"/>
+    <col min="2" max="3" width="22.7079646017699" style="13" customWidth="1"/>
+    <col min="4" max="4" width="20.7079646017699" style="13" customWidth="1"/>
+    <col min="5" max="5" width="17.7079646017699" style="13" customWidth="1"/>
+    <col min="6" max="16384" width="11" style="13"/>
   </cols>
   <sheetData>
-    <row r="1" ht="18" spans="1:1">
-      <c r="A1" s="1" t="s">
+    <row r="1" ht="15" spans="1:1">
+      <c r="A1" s="19" t="s">
         <v>323</v>
       </c>
     </row>
-    <row r="2" ht="26.25" spans="1:1">
-      <c r="A2" s="4" t="s">
+    <row r="2" ht="30.75" spans="1:1">
+      <c r="A2" s="20" t="s">
         <v>324</v>
       </c>
     </row>
-    <row r="4" spans="1:5">
-      <c r="A4" s="2" t="s">
+    <row r="4" ht="15" spans="1:5">
+      <c r="A4" s="7" t="s">
         <v>301</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="B4" s="7" t="s">
         <v>311</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="C4" s="7" t="s">
         <v>312</v>
       </c>
-      <c r="D4" s="2" t="s">
+      <c r="D4" s="7" t="s">
         <v>313</v>
       </c>
-      <c r="E4" s="2" t="s">
+      <c r="E4" s="7" t="s">
         <v>314</v>
       </c>
     </row>
-    <row r="5" spans="1:5">
-      <c r="A5" s="3" t="s">
+    <row r="5" ht="15.4" spans="1:5">
+      <c r="A5" s="14" t="s">
         <v>311</v>
       </c>
-      <c r="B5" s="6">
+      <c r="B5" s="16">
         <v>1</v>
       </c>
-      <c r="C5" s="6">
+      <c r="C5" s="16">
         <v>0.611894388831612</v>
       </c>
-      <c r="D5" s="6">
+      <c r="D5" s="16">
         <v>0.527864045000421</v>
       </c>
-      <c r="E5" s="6">
+      <c r="E5" s="16">
         <v>0.2004877356893</v>
       </c>
     </row>
-    <row r="6" spans="1:5">
-      <c r="A6" s="3" t="s">
+    <row r="6" ht="15.4" spans="1:5">
+      <c r="A6" s="14" t="s">
         <v>312</v>
       </c>
-      <c r="B6" s="6">
+      <c r="B6" s="16">
         <v>0.611894388831612</v>
       </c>
-      <c r="C6" s="6">
+      <c r="C6" s="16">
         <v>1</v>
       </c>
-      <c r="D6" s="6">
+      <c r="D6" s="16">
         <v>0.258200890033433</v>
       </c>
-      <c r="E6" s="6">
+      <c r="E6" s="16">
         <v>0.337041968972851</v>
       </c>
     </row>
-    <row r="7" spans="1:5">
-      <c r="A7" s="3" t="s">
+    <row r="7" ht="15.4" spans="1:5">
+      <c r="A7" s="14" t="s">
         <v>313</v>
       </c>
-      <c r="B7" s="6">
+      <c r="B7" s="16">
         <v>0.527864045000421</v>
       </c>
-      <c r="C7" s="6">
+      <c r="C7" s="16">
         <v>0.258200890033433</v>
       </c>
-      <c r="D7" s="6">
+      <c r="D7" s="16">
         <v>1</v>
       </c>
-      <c r="E7" s="6">
+      <c r="E7" s="16">
         <v>0.342676122689269</v>
       </c>
     </row>
-    <row r="8" spans="1:5">
-      <c r="A8" s="3" t="s">
+    <row r="8" ht="15.4" spans="1:5">
+      <c r="A8" s="14" t="s">
         <v>314</v>
       </c>
-      <c r="B8" s="6">
+      <c r="B8" s="16">
         <v>0.2004877356893</v>
       </c>
-      <c r="C8" s="6">
+      <c r="C8" s="16">
         <v>0.337041968972851</v>
       </c>
-      <c r="D8" s="6">
+      <c r="D8" s="16">
         <v>0.342676122689269</v>
       </c>
-      <c r="E8" s="6">
+      <c r="E8" s="16">
         <v>1</v>
       </c>
     </row>
@@ -3408,224 +3797,226 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:H11"/>
-  <sheetFormatPr defaultColWidth="11" defaultRowHeight="14.25" outlineLevelCol="7"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.35" outlineLevelCol="7"/>
   <cols>
-    <col min="1" max="3" width="35.7079646017699" customWidth="1"/>
-    <col min="4" max="4" width="10.7079646017699" customWidth="1"/>
-    <col min="5" max="5" width="12.7079646017699" customWidth="1"/>
-    <col min="6" max="8" width="11.7079646017699" customWidth="1"/>
+    <col min="1" max="1" width="37.1769911504425" style="13" customWidth="1"/>
+    <col min="2" max="3" width="35.7079646017699" style="13" customWidth="1"/>
+    <col min="4" max="4" width="10.7079646017699" style="13" customWidth="1"/>
+    <col min="5" max="5" width="17.5221238938053" style="13" customWidth="1"/>
+    <col min="6" max="8" width="11.7079646017699" style="13" customWidth="1"/>
+    <col min="9" max="16384" width="11" style="13"/>
   </cols>
   <sheetData>
-    <row r="1" ht="18" spans="1:1">
-      <c r="A1" s="1" t="s">
+    <row r="1" ht="15" spans="1:1">
+      <c r="A1" s="19" t="s">
         <v>325</v>
       </c>
     </row>
-    <row r="4" spans="1:8">
-      <c r="A4" s="2" t="s">
+    <row r="4" ht="30" spans="1:8">
+      <c r="A4" s="7" t="s">
         <v>326</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="B4" s="7" t="s">
         <v>327</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="C4" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="D4" s="2" t="s">
+      <c r="D4" s="7" t="s">
         <v>127</v>
       </c>
-      <c r="E4" s="2" t="s">
+      <c r="E4" s="7" t="s">
         <v>319</v>
       </c>
-      <c r="F4" s="2" t="s">
+      <c r="F4" s="7" t="s">
         <v>320</v>
       </c>
-      <c r="G4" s="2" t="s">
+      <c r="G4" s="7" t="s">
         <v>321</v>
       </c>
-      <c r="H4" s="2" t="s">
+      <c r="H4" s="7" t="s">
         <v>322</v>
       </c>
     </row>
-    <row r="5" spans="1:8">
-      <c r="A5" s="3" t="s">
+    <row r="5" ht="30.75" spans="1:8">
+      <c r="A5" s="14" t="s">
         <v>328</v>
       </c>
-      <c r="B5" s="3" t="s">
+      <c r="B5" s="14" t="s">
         <v>329</v>
       </c>
-      <c r="C5" s="3" t="s">
+      <c r="C5" s="14" t="s">
         <v>330</v>
       </c>
-      <c r="D5" s="5">
-        <v>31</v>
-      </c>
-      <c r="E5" s="6">
+      <c r="D5" s="15">
+        <v>31</v>
+      </c>
+      <c r="E5" s="16">
         <v>0.630387116088968</v>
       </c>
-      <c r="F5" s="6">
+      <c r="F5" s="16">
         <v>1833.27990419872</v>
       </c>
-      <c r="G5" s="8">
+      <c r="G5" s="18">
         <v>0.000144113796206363</v>
       </c>
-      <c r="H5" s="8">
+      <c r="H5" s="18">
         <v>0.00100879657344454</v>
       </c>
     </row>
-    <row r="6" spans="1:8">
-      <c r="A6" s="3" t="s">
+    <row r="6" ht="15.4" spans="1:8">
+      <c r="A6" s="14" t="s">
         <v>314</v>
       </c>
-      <c r="B6" s="3" t="s">
+      <c r="B6" s="14" t="s">
         <v>329</v>
       </c>
-      <c r="C6" s="3" t="s">
+      <c r="C6" s="14" t="s">
         <v>331</v>
       </c>
-      <c r="D6" s="5">
-        <v>31</v>
-      </c>
-      <c r="E6" s="6">
+      <c r="D6" s="15">
+        <v>31</v>
+      </c>
+      <c r="E6" s="16">
         <v>0.565575001657624</v>
       </c>
-      <c r="F6" s="6">
+      <c r="F6" s="16">
         <v>2154.74799177819</v>
       </c>
-      <c r="G6" s="8">
+      <c r="G6" s="18">
         <v>0.00091406785685768</v>
       </c>
-      <c r="H6" s="8">
+      <c r="H6" s="18">
         <v>0.00319923749900188</v>
       </c>
     </row>
-    <row r="7" spans="1:8">
-      <c r="A7" s="3" t="s">
+    <row r="7" ht="15.4" spans="1:8">
+      <c r="A7" s="14" t="s">
         <v>328</v>
       </c>
-      <c r="B7" s="3" t="s">
+      <c r="B7" s="14" t="s">
         <v>332</v>
       </c>
-      <c r="C7" s="3" t="s">
+      <c r="C7" s="14" t="s">
         <v>333</v>
       </c>
-      <c r="D7" s="5">
-        <v>31</v>
-      </c>
-      <c r="E7" s="6">
+      <c r="D7" s="15">
+        <v>31</v>
+      </c>
+      <c r="E7" s="16">
         <v>0.546957284096226</v>
       </c>
-      <c r="F7" s="6">
+      <c r="F7" s="16">
         <v>2247.09187088272</v>
       </c>
-      <c r="G7" s="8">
+      <c r="G7" s="18">
         <v>0.00145246829132102</v>
       </c>
-      <c r="H7" s="8">
+      <c r="H7" s="18">
         <v>0.00338909267974905</v>
       </c>
     </row>
-    <row r="8" spans="1:8">
-      <c r="A8" s="3" t="s">
+    <row r="8" ht="15.4" spans="1:8">
+      <c r="A8" s="14" t="s">
         <v>328</v>
       </c>
-      <c r="B8" s="3" t="s">
+      <c r="B8" s="14" t="s">
         <v>314</v>
       </c>
-      <c r="C8" s="3" t="s">
+      <c r="C8" s="14" t="s">
         <v>334</v>
       </c>
-      <c r="D8" s="5">
-        <v>31</v>
-      </c>
-      <c r="E8" s="6">
+      <c r="D8" s="15">
+        <v>31</v>
+      </c>
+      <c r="E8" s="16">
         <v>0.492406556952279</v>
       </c>
-      <c r="F8" s="6">
+      <c r="F8" s="16">
         <v>2517.66347751669</v>
       </c>
-      <c r="G8" s="8">
+      <c r="G8" s="18">
         <v>0.00489336442983224</v>
       </c>
-      <c r="H8" s="8">
+      <c r="H8" s="18">
         <v>0.00856338775220642</v>
       </c>
     </row>
-    <row r="9" spans="1:8">
-      <c r="A9" s="3" t="s">
+    <row r="9" ht="15.4" spans="1:8">
+      <c r="A9" s="14" t="s">
         <v>335</v>
       </c>
-      <c r="B9" s="3" t="s">
+      <c r="B9" s="14" t="s">
         <v>328</v>
       </c>
-      <c r="C9" s="3" t="s">
+      <c r="C9" s="14" t="s">
         <v>336</v>
       </c>
-      <c r="D9" s="5">
-        <v>31</v>
-      </c>
-      <c r="E9" s="6">
+      <c r="D9" s="15">
+        <v>31</v>
+      </c>
+      <c r="E9" s="16">
         <v>-0.465980802864486</v>
       </c>
-      <c r="F9" s="6">
+      <c r="F9" s="16">
         <v>7271.26478220785</v>
       </c>
-      <c r="G9" s="8">
+      <c r="G9" s="18">
         <v>0.00824100868360479</v>
       </c>
-      <c r="H9" s="8">
+      <c r="H9" s="18">
         <v>0.0115374121570467</v>
       </c>
     </row>
-    <row r="10" ht="28.5" spans="1:8">
-      <c r="A10" s="3" t="s">
+    <row r="10" ht="30.75" spans="1:8">
+      <c r="A10" s="14" t="s">
         <v>329</v>
       </c>
-      <c r="B10" s="3" t="s">
+      <c r="B10" s="14" t="s">
         <v>337</v>
       </c>
-      <c r="C10" s="3" t="s">
+      <c r="C10" s="14" t="s">
         <v>338</v>
       </c>
-      <c r="D10" s="5">
+      <c r="D10" s="15">
         <v>27</v>
       </c>
-      <c r="E10" s="6">
+      <c r="E10" s="16">
         <v>-0.381202777704913</v>
       </c>
-      <c r="F10" s="6">
+      <c r="F10" s="16">
         <v>4524.82029976129</v>
       </c>
-      <c r="G10" s="8">
+      <c r="G10" s="18">
         <v>0.0497789626082451</v>
       </c>
-      <c r="H10" s="8">
+      <c r="H10" s="18">
         <v>0.058075456376286</v>
       </c>
     </row>
-    <row r="11" spans="1:8">
-      <c r="A11" s="3" t="s">
+    <row r="11" ht="15.4" spans="1:8">
+      <c r="A11" s="14" t="s">
         <v>332</v>
       </c>
-      <c r="B11" s="3" t="s">
+      <c r="B11" s="14" t="s">
         <v>314</v>
       </c>
-      <c r="C11" s="3" t="s">
+      <c r="C11" s="14" t="s">
         <v>339</v>
       </c>
-      <c r="D11" s="5">
-        <v>31</v>
-      </c>
-      <c r="E11" s="6">
+      <c r="D11" s="15">
+        <v>31</v>
+      </c>
+      <c r="E11" s="16">
         <v>0.256652943127277</v>
       </c>
-      <c r="F11" s="6">
+      <c r="F11" s="16">
         <v>3687.0014020887</v>
       </c>
-      <c r="G11" s="8">
+      <c r="G11" s="18">
         <v>0.163397910797378</v>
       </c>
-      <c r="H11" s="8">
+      <c r="H11" s="18">
         <v>0.163397910797378</v>
       </c>
     </row>
@@ -3643,234 +4034,236 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:M8"/>
-  <sheetFormatPr defaultColWidth="11" defaultRowHeight="14.25" outlineLevelRow="7"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.35" outlineLevelRow="7"/>
   <cols>
-    <col min="1" max="2" width="35.7079646017699" customWidth="1"/>
-    <col min="3" max="3" width="10.7079646017699" customWidth="1"/>
-    <col min="4" max="4" width="19.7079646017699" customWidth="1"/>
-    <col min="5" max="5" width="22.7079646017699" customWidth="1"/>
-    <col min="6" max="6" width="20.7079646017699" customWidth="1"/>
-    <col min="7" max="7" width="23.7079646017699" customWidth="1"/>
-    <col min="8" max="8" width="11.7079646017699" customWidth="1"/>
-    <col min="9" max="9" width="14.7079646017699" customWidth="1"/>
-    <col min="10" max="10" width="15.7079646017699" customWidth="1"/>
-    <col min="11" max="11" width="11.7079646017699" customWidth="1"/>
-    <col min="12" max="12" width="35.7079646017699" customWidth="1"/>
-    <col min="13" max="13" width="11.7079646017699" customWidth="1"/>
+    <col min="1" max="1" width="44.6814159292035" style="5" customWidth="1"/>
+    <col min="2" max="2" width="35.7079646017699" style="5" customWidth="1"/>
+    <col min="3" max="3" width="10.7079646017699" style="5" customWidth="1"/>
+    <col min="4" max="4" width="19.7079646017699" style="5" customWidth="1"/>
+    <col min="5" max="5" width="22.7079646017699" style="5" customWidth="1"/>
+    <col min="6" max="6" width="20.7079646017699" style="5" customWidth="1"/>
+    <col min="7" max="7" width="23.7079646017699" style="5" customWidth="1"/>
+    <col min="8" max="8" width="11.7079646017699" style="5" customWidth="1"/>
+    <col min="9" max="9" width="14.7079646017699" style="5" customWidth="1"/>
+    <col min="10" max="10" width="15.7079646017699" style="5" customWidth="1"/>
+    <col min="11" max="11" width="11.7079646017699" style="5" customWidth="1"/>
+    <col min="12" max="12" width="35.7079646017699" style="5" customWidth="1"/>
+    <col min="13" max="13" width="11.7079646017699" style="5" customWidth="1"/>
+    <col min="14" max="16384" width="11" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" ht="18" spans="1:1">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:1">
+      <c r="A1" s="9" t="s">
         <v>340</v>
       </c>
     </row>
-    <row r="2" ht="26.25" spans="1:1">
-      <c r="A2" s="4" t="s">
+    <row r="2" ht="30.75" spans="1:1">
+      <c r="A2" s="10" t="s">
         <v>341</v>
       </c>
     </row>
-    <row r="4" spans="1:13">
-      <c r="A4" s="2" t="s">
+    <row r="4" s="13" customFormat="1" ht="15" spans="1:13">
+      <c r="A4" s="7" t="s">
         <v>326</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="B4" s="7" t="s">
         <v>342</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="C4" s="7" t="s">
         <v>127</v>
       </c>
-      <c r="D4" s="2" t="s">
+      <c r="D4" s="7" t="s">
         <v>343</v>
       </c>
-      <c r="E4" s="2" t="s">
+      <c r="E4" s="7" t="s">
         <v>344</v>
       </c>
-      <c r="F4" s="2" t="s">
+      <c r="F4" s="7" t="s">
         <v>345</v>
       </c>
-      <c r="G4" s="2" t="s">
+      <c r="G4" s="7" t="s">
         <v>346</v>
       </c>
-      <c r="H4" s="2" t="s">
+      <c r="H4" s="7" t="s">
         <v>347</v>
       </c>
-      <c r="I4" s="2" t="s">
+      <c r="I4" s="7" t="s">
         <v>348</v>
       </c>
-      <c r="J4" s="2" t="s">
+      <c r="J4" s="7" t="s">
         <v>349</v>
       </c>
-      <c r="K4" s="2" t="s">
+      <c r="K4" s="7" t="s">
         <v>321</v>
       </c>
-      <c r="L4" s="2" t="s">
+      <c r="L4" s="7" t="s">
         <v>350</v>
       </c>
-      <c r="M4" s="2" t="s">
+      <c r="M4" s="7" t="s">
         <v>322</v>
       </c>
     </row>
-    <row r="5" ht="28.5" spans="1:13">
-      <c r="A5" s="3" t="s">
+    <row r="5" s="13" customFormat="1" ht="30.75" spans="1:13">
+      <c r="A5" s="14" t="s">
         <v>351</v>
       </c>
-      <c r="B5" s="3" t="s">
+      <c r="B5" s="14" t="s">
         <v>352</v>
       </c>
-      <c r="C5" s="5">
-        <v>31</v>
-      </c>
-      <c r="D5" s="5">
+      <c r="C5" s="15">
+        <v>31</v>
+      </c>
+      <c r="D5" s="15">
         <v>21</v>
       </c>
-      <c r="E5" s="5">
+      <c r="E5" s="15">
         <v>1</v>
       </c>
-      <c r="F5" s="5">
+      <c r="F5" s="15">
         <v>2</v>
       </c>
-      <c r="G5" s="5">
+      <c r="G5" s="15">
         <v>7</v>
       </c>
-      <c r="H5" s="7">
+      <c r="H5" s="17">
         <v>55.1734750845149</v>
       </c>
-      <c r="I5" s="7">
+      <c r="I5" s="17">
         <v>4.42768421126716</v>
       </c>
-      <c r="J5" s="7">
+      <c r="J5" s="17">
         <v>3352.34638272578</v>
       </c>
-      <c r="K5" s="8">
+      <c r="K5" s="18">
         <v>0.00010153732066969</v>
       </c>
-      <c r="L5" s="3" t="s">
+      <c r="L5" s="14" t="s">
         <v>353</v>
       </c>
-      <c r="M5" s="8">
+      <c r="M5" s="18">
         <v>0.00040614928267876</v>
       </c>
     </row>
-    <row r="6" ht="28.5" spans="1:13">
-      <c r="A6" s="3" t="s">
+    <row r="6" s="13" customFormat="1" ht="30.75" spans="1:13">
+      <c r="A6" s="14" t="s">
         <v>354</v>
       </c>
-      <c r="B6" s="3" t="s">
+      <c r="B6" s="14" t="s">
         <v>355</v>
       </c>
-      <c r="C6" s="5">
-        <v>31</v>
-      </c>
-      <c r="D6" s="5">
+      <c r="C6" s="15">
+        <v>31</v>
+      </c>
+      <c r="D6" s="15">
         <v>21</v>
       </c>
-      <c r="E6" s="5">
+      <c r="E6" s="15">
         <v>2</v>
       </c>
-      <c r="F6" s="5">
+      <c r="F6" s="15">
         <v>2</v>
       </c>
-      <c r="G6" s="5">
+      <c r="G6" s="15">
         <v>6</v>
       </c>
-      <c r="H6" s="7">
+      <c r="H6" s="17">
         <v>25.7639544279223</v>
       </c>
-      <c r="I6" s="7">
+      <c r="I6" s="17">
         <v>2.6662369890551</v>
       </c>
-      <c r="J6" s="7">
+      <c r="J6" s="17">
         <v>449.049978094132</v>
       </c>
-      <c r="K6" s="8">
+      <c r="K6" s="18">
         <v>0.000921441677837674</v>
       </c>
-      <c r="L6" s="3" t="s">
+      <c r="L6" s="14" t="s">
         <v>353</v>
       </c>
-      <c r="M6" s="8">
+      <c r="M6" s="18">
         <v>0.00184288335567535</v>
       </c>
     </row>
-    <row r="7" ht="28.5" spans="1:13">
-      <c r="A7" s="3" t="s">
+    <row r="7" s="13" customFormat="1" ht="30.75" spans="1:13">
+      <c r="A7" s="14" t="s">
         <v>356</v>
       </c>
-      <c r="B7" s="3" t="s">
+      <c r="B7" s="14" t="s">
         <v>357</v>
       </c>
-      <c r="C7" s="5">
-        <v>31</v>
-      </c>
-      <c r="D7" s="5">
+      <c r="C7" s="15">
+        <v>31</v>
+      </c>
+      <c r="D7" s="15">
         <v>22</v>
       </c>
-      <c r="E7" s="5">
+      <c r="E7" s="15">
         <v>5</v>
       </c>
-      <c r="F7" s="5">
+      <c r="F7" s="15">
         <v>1</v>
       </c>
-      <c r="G7" s="5">
+      <c r="G7" s="15">
         <v>3</v>
       </c>
-      <c r="H7" s="7">
+      <c r="H7" s="17">
         <v>11.7624332757672</v>
       </c>
-      <c r="I7" s="7">
+      <c r="I7" s="17">
         <v>0.771024663171752</v>
       </c>
-      <c r="J7" s="7">
+      <c r="J7" s="17">
         <v>719.133843195589</v>
       </c>
-      <c r="K7" s="8">
+      <c r="K7" s="18">
         <v>0.0431590656284761</v>
       </c>
-      <c r="L7" s="3" t="s">
+      <c r="L7" s="14" t="s">
         <v>353</v>
       </c>
-      <c r="M7" s="8">
+      <c r="M7" s="18">
         <v>0.0575454208379682</v>
       </c>
     </row>
-    <row r="8" ht="28.5" spans="1:13">
-      <c r="A8" s="3" t="s">
+    <row r="8" s="13" customFormat="1" ht="30.75" spans="1:13">
+      <c r="A8" s="14" t="s">
         <v>358</v>
       </c>
-      <c r="B8" s="3" t="s">
+      <c r="B8" s="14" t="s">
         <v>359</v>
       </c>
-      <c r="C8" s="5">
-        <v>31</v>
-      </c>
-      <c r="D8" s="5">
+      <c r="C8" s="15">
+        <v>31</v>
+      </c>
+      <c r="D8" s="15">
         <v>14</v>
       </c>
-      <c r="E8" s="5">
+      <c r="E8" s="15">
         <v>2</v>
       </c>
-      <c r="F8" s="5">
+      <c r="F8" s="15">
         <v>9</v>
       </c>
-      <c r="G8" s="5">
+      <c r="G8" s="15">
         <v>6</v>
       </c>
-      <c r="H8" s="7">
+      <c r="H8" s="17">
         <v>4.43411408829531</v>
       </c>
-      <c r="I8" s="7">
+      <c r="I8" s="17">
         <v>0.614418477197649</v>
       </c>
-      <c r="J8" s="7">
+      <c r="J8" s="17">
         <v>54.3904116460745</v>
       </c>
-      <c r="K8" s="8">
+      <c r="K8" s="18">
         <v>0.11338524286244</v>
       </c>
-      <c r="L8" s="3" t="s">
+      <c r="L8" s="14" t="s">
         <v>353</v>
       </c>
-      <c r="M8" s="8">
+      <c r="M8" s="18">
         <v>0.11338524286244</v>
       </c>
     </row>
@@ -3887,296 +4280,303 @@
 <file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:N9"/>
-  <sheetFormatPr defaultColWidth="11" defaultRowHeight="14.25"/>
+  <dimension ref="A1:O9"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.35"/>
   <cols>
-    <col min="1" max="2" width="35.7079646017699" customWidth="1"/>
-    <col min="3" max="3" width="10.7079646017699" customWidth="1"/>
-    <col min="4" max="4" width="11.7079646017699" customWidth="1"/>
-    <col min="5" max="5" width="23.7079646017699" customWidth="1"/>
-    <col min="6" max="7" width="11.7079646017699" customWidth="1"/>
-    <col min="8" max="8" width="14.7079646017699" customWidth="1"/>
-    <col min="9" max="9" width="15.7079646017699" customWidth="1"/>
-    <col min="10" max="10" width="15.2477876106195" customWidth="1"/>
-    <col min="11" max="11" width="14.7079646017699" customWidth="1"/>
-    <col min="12" max="12" width="11.7079646017699" customWidth="1"/>
-    <col min="13" max="13" width="9.70796460176991" customWidth="1"/>
-    <col min="14" max="14" width="15.2477876106195" customWidth="1"/>
+    <col min="1" max="1" width="55.3008849557522" style="5" customWidth="1"/>
+    <col min="2" max="2" width="35.7079646017699" style="5" customWidth="1"/>
+    <col min="3" max="3" width="10.7079646017699" style="5" customWidth="1"/>
+    <col min="4" max="4" width="11.7079646017699" style="5" customWidth="1"/>
+    <col min="5" max="5" width="23.7079646017699" style="5" customWidth="1"/>
+    <col min="6" max="7" width="11.7079646017699" style="5" customWidth="1"/>
+    <col min="8" max="8" width="14.7079646017699" style="5" customWidth="1"/>
+    <col min="9" max="9" width="15.7079646017699" style="5" customWidth="1"/>
+    <col min="10" max="10" width="15.2477876106195" style="5" customWidth="1"/>
+    <col min="11" max="11" width="14.7079646017699" style="5" customWidth="1"/>
+    <col min="12" max="12" width="11.7079646017699" style="5" customWidth="1"/>
+    <col min="13" max="13" width="9.70796460176991" style="5" customWidth="1"/>
+    <col min="14" max="14" width="15.2477876106195" style="5" customWidth="1"/>
+    <col min="15" max="16384" width="11" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" ht="18" spans="1:1">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:1">
+      <c r="A1" s="9" t="s">
         <v>360</v>
       </c>
     </row>
-    <row r="2" ht="26.25" spans="1:1">
-      <c r="A2" s="4" t="s">
+    <row r="2" ht="46.15" spans="1:1">
+      <c r="A2" s="10" t="s">
         <v>361</v>
       </c>
     </row>
-    <row r="4" spans="1:14">
-      <c r="A4" s="2" t="s">
+    <row r="4" s="13" customFormat="1" ht="30" spans="1:14">
+      <c r="A4" s="7" t="s">
         <v>326</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="B4" s="7" t="s">
         <v>342</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="C4" s="7" t="s">
         <v>127</v>
       </c>
-      <c r="D4" s="2" t="s">
+      <c r="D4" s="7" t="s">
         <v>362</v>
       </c>
-      <c r="E4" s="2" t="s">
+      <c r="E4" s="7" t="s">
         <v>363</v>
       </c>
-      <c r="F4" s="2" t="s">
+      <c r="F4" s="7" t="s">
         <v>364</v>
       </c>
-      <c r="G4" s="2" t="s">
+      <c r="G4" s="7" t="s">
         <v>347</v>
       </c>
-      <c r="H4" s="2" t="s">
+      <c r="H4" s="7" t="s">
         <v>348</v>
       </c>
-      <c r="I4" s="2" t="s">
+      <c r="I4" s="7" t="s">
         <v>349</v>
       </c>
-      <c r="J4" s="2" t="s">
+      <c r="J4" s="7" t="s">
         <v>321</v>
       </c>
-      <c r="K4" s="2" t="s">
+      <c r="K4" s="7" t="s">
         <v>365</v>
       </c>
-      <c r="L4" s="2" t="s">
+      <c r="L4" s="7" t="s">
         <v>366</v>
       </c>
-      <c r="M4" s="2" t="s">
+      <c r="M4" s="7" t="s">
         <v>367</v>
       </c>
-      <c r="N4" s="2" t="s">
+      <c r="N4" s="7" t="s">
         <v>322</v>
       </c>
     </row>
-    <row r="5" ht="28.5" spans="1:14">
-      <c r="A5" s="3" t="s">
+    <row r="5" ht="30.75" spans="1:15">
+      <c r="A5" s="14" t="s">
         <v>328</v>
       </c>
-      <c r="B5" s="3" t="s">
+      <c r="B5" s="14" t="s">
         <v>368</v>
       </c>
-      <c r="C5" s="5">
-        <v>31</v>
-      </c>
-      <c r="D5" s="6">
+      <c r="C5" s="15">
+        <v>31</v>
+      </c>
+      <c r="D5" s="16">
         <v>2.45640166773709</v>
       </c>
-      <c r="E5" s="6">
+      <c r="E5" s="16">
         <v>0.918769011925872</v>
       </c>
-      <c r="F5" s="6">
+      <c r="F5" s="16">
         <v>2.67357914323657</v>
       </c>
-      <c r="G5" s="7">
+      <c r="G5" s="17">
         <v>11.6627694250978</v>
       </c>
-      <c r="H5" s="7">
+      <c r="H5" s="17">
         <v>1.92638943973254</v>
       </c>
-      <c r="I5" s="7">
+      <c r="I5" s="17">
         <v>70.6088747464695</v>
       </c>
-      <c r="J5" s="8">
+      <c r="J5" s="18">
         <v>0.00750465659013394</v>
       </c>
-      <c r="K5" s="6">
+      <c r="K5" s="16">
         <v>-10.1782343072915</v>
       </c>
-      <c r="L5" s="7">
+      <c r="L5" s="17">
         <v>24.356468614583</v>
       </c>
-      <c r="M5" t="b">
+      <c r="M5" s="13" t="b">
         <v>1</v>
       </c>
-      <c r="N5" s="8">
+      <c r="N5" s="18">
         <v>0.0125077609835566</v>
       </c>
-    </row>
-    <row r="6" spans="1:14">
-      <c r="A6" s="3" t="s">
+      <c r="O5" s="13"/>
+    </row>
+    <row r="6" ht="15.4" spans="1:15">
+      <c r="A6" s="14" t="s">
         <v>332</v>
       </c>
-      <c r="B6" s="3" t="s">
+      <c r="B6" s="14" t="s">
         <v>369</v>
       </c>
-      <c r="C6" s="5">
-        <v>31</v>
-      </c>
-      <c r="D6" s="6">
+      <c r="C6" s="15">
+        <v>31</v>
+      </c>
+      <c r="D6" s="16">
         <v>0.876522627799507</v>
       </c>
-      <c r="E6" s="6">
+      <c r="E6" s="16">
         <v>0.510003033682723</v>
       </c>
-      <c r="F6" s="6">
+      <c r="F6" s="16">
         <v>1.71866159593239</v>
       </c>
-      <c r="G6" s="7">
+      <c r="G6" s="17">
         <v>2.40253067035988</v>
       </c>
-      <c r="H6" s="7">
+      <c r="H6" s="17">
         <v>0.884206231302264</v>
       </c>
-      <c r="I6" s="7">
+      <c r="I6" s="17">
         <v>6.52806259182165</v>
       </c>
-      <c r="J6" s="8">
+      <c r="J6" s="18">
         <v>0.0856760087597529</v>
       </c>
-      <c r="K6" s="6">
+      <c r="K6" s="16">
         <v>-15.8123103022365</v>
       </c>
-      <c r="L6" s="7">
+      <c r="L6" s="17">
         <v>35.6246206044729</v>
       </c>
-      <c r="M6" t="b">
+      <c r="M6" s="13" t="b">
         <v>1</v>
       </c>
-      <c r="N6" s="8">
+      <c r="N6" s="18">
         <v>0.0856760087597529</v>
       </c>
-    </row>
-    <row r="7" spans="1:14">
-      <c r="A7" s="3" t="s">
+      <c r="O6" s="13"/>
+    </row>
+    <row r="7" ht="15.4" spans="1:15">
+      <c r="A7" s="14" t="s">
         <v>314</v>
       </c>
-      <c r="B7" s="3" t="s">
+      <c r="B7" s="14" t="s">
         <v>370</v>
       </c>
-      <c r="C7" s="5">
-        <v>31</v>
-      </c>
-      <c r="D7" s="6">
+      <c r="C7" s="15">
+        <v>31</v>
+      </c>
+      <c r="D7" s="16">
         <v>1.62269786068039</v>
       </c>
-      <c r="E7" s="6">
+      <c r="E7" s="16">
         <v>0.819391528105953</v>
       </c>
-      <c r="F7" s="6">
+      <c r="F7" s="16">
         <v>1.980369341176</v>
       </c>
-      <c r="G7" s="7">
+      <c r="G7" s="17">
         <v>5.06674125613011</v>
       </c>
-      <c r="H7" s="7">
+      <c r="H7" s="17">
         <v>1.01686053746018</v>
       </c>
-      <c r="I7" s="7">
+      <c r="I7" s="17">
         <v>25.246202415025</v>
       </c>
-      <c r="J7" s="8">
+      <c r="J7" s="18">
         <v>0.0476620423597859</v>
       </c>
-      <c r="K7" s="6">
+      <c r="K7" s="16">
         <v>-13.7434881886219</v>
       </c>
-      <c r="L7" s="7">
+      <c r="L7" s="17">
         <v>31.4869763772439</v>
       </c>
-      <c r="M7" t="b">
+      <c r="M7" s="13" t="b">
         <v>1</v>
       </c>
-      <c r="N7" s="8">
+      <c r="N7" s="18">
         <v>0.0595775529497324</v>
       </c>
-    </row>
-    <row r="8" ht="28.5" spans="1:14">
-      <c r="A8" s="3" t="s">
+      <c r="O7" s="13"/>
+    </row>
+    <row r="8" ht="30.75" spans="1:15">
+      <c r="A8" s="14" t="s">
         <v>329</v>
       </c>
-      <c r="B8" s="3" t="s">
+      <c r="B8" s="14" t="s">
         <v>371</v>
       </c>
-      <c r="C8" s="5">
-        <v>31</v>
-      </c>
-      <c r="D8" s="6">
+      <c r="C8" s="15">
+        <v>31</v>
+      </c>
+      <c r="D8" s="16">
         <v>2.32589840120903</v>
       </c>
-      <c r="E8" s="6">
+      <c r="E8" s="16">
         <v>0.833517155873191</v>
       </c>
-      <c r="F8" s="6">
+      <c r="F8" s="16">
         <v>2.79046254155672</v>
       </c>
-      <c r="G8" s="7">
+      <c r="G8" s="17">
         <v>10.2358718758839</v>
       </c>
-      <c r="H8" s="7">
+      <c r="H8" s="17">
         <v>1.99817606147668</v>
       </c>
-      <c r="I8" s="7">
+      <c r="I8" s="17">
         <v>52.4343550498156</v>
       </c>
-      <c r="J8" s="8">
+      <c r="J8" s="18">
         <v>0.00526327901260575</v>
       </c>
-      <c r="K8" s="6">
+      <c r="K8" s="16">
         <v>-6.69020161122829</v>
       </c>
-      <c r="L8" s="7">
+      <c r="L8" s="17">
         <v>17.3804032224566</v>
       </c>
-      <c r="M8" t="b">
+      <c r="M8" s="13" t="b">
         <v>1</v>
       </c>
-      <c r="N8" s="8">
+      <c r="N8" s="18">
         <v>0.0125077609835566</v>
       </c>
-    </row>
-    <row r="9" spans="1:14">
-      <c r="A9" s="3" t="s">
+      <c r="O8" s="13"/>
+    </row>
+    <row r="9" ht="15.4" spans="1:15">
+      <c r="A9" s="14" t="s">
         <v>372</v>
       </c>
-      <c r="B9" s="3" t="s">
+      <c r="B9" s="14" t="s">
         <v>373</v>
       </c>
-      <c r="C9" s="5">
-        <v>31</v>
-      </c>
-      <c r="D9" s="6">
+      <c r="C9" s="15">
+        <v>31</v>
+      </c>
+      <c r="D9" s="16">
         <v>1.27503409960416</v>
       </c>
-      <c r="E9" s="6">
+      <c r="E9" s="16">
         <v>0.468050873896133</v>
       </c>
-      <c r="F9" s="6">
+      <c r="F9" s="16">
         <v>2.72413570984402</v>
       </c>
-      <c r="G9" s="7">
+      <c r="G9" s="17">
         <v>3.57882344448371</v>
       </c>
-      <c r="H9" s="7">
+      <c r="H9" s="17">
         <v>1.42999542338302</v>
       </c>
-      <c r="I9" s="7">
+      <c r="I9" s="17">
         <v>8.95665611046904</v>
       </c>
-      <c r="J9" s="8">
+      <c r="J9" s="18">
         <v>0.00644700092664399</v>
       </c>
-      <c r="K9" s="6">
+      <c r="K9" s="16">
         <v>-9.97850357047346</v>
       </c>
-      <c r="L9" s="7">
+      <c r="L9" s="17">
         <v>23.9570071409469</v>
       </c>
-      <c r="M9" t="b">
+      <c r="M9" s="13" t="b">
         <v>1</v>
       </c>
-      <c r="N9" s="8">
+      <c r="N9" s="18">
         <v>0.0125077609835566</v>
       </c>
+      <c r="O9" s="13"/>
     </row>
   </sheetData>
   <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A4:N9" etc:filterBottomFollowUsedRange="0">
@@ -4191,184 +4591,135 @@
 <file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:F11"/>
-  <sheetFormatPr defaultColWidth="11" defaultRowHeight="14.25" outlineLevelCol="5"/>
+  <dimension ref="A1:D11"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.35" outlineLevelCol="3"/>
   <cols>
-    <col min="1" max="6" width="35.7079646017699" customWidth="1"/>
+    <col min="1" max="4" width="35.7079646017699" style="5" customWidth="1"/>
+    <col min="5" max="16384" width="11" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" ht="18" spans="1:1">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:1">
+      <c r="A1" s="9" t="s">
         <v>374</v>
       </c>
     </row>
-    <row r="2" ht="26.25" spans="1:1">
-      <c r="A2" s="4" t="s">
+    <row r="2" spans="1:1">
+      <c r="A2" s="10"/>
+    </row>
+    <row r="4" spans="1:4">
+      <c r="A4" s="11" t="s">
+        <v>54</v>
+      </c>
+      <c r="B4" s="11" t="s">
         <v>375</v>
       </c>
-    </row>
-    <row r="4" spans="1:6">
-      <c r="A4" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="B4" s="2" t="s">
+      <c r="C4" s="11" t="s">
         <v>376</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="D4" s="11" t="s">
         <v>377</v>
       </c>
-      <c r="D4" s="2" t="s">
+    </row>
+    <row r="5" ht="61.5" spans="1:4">
+      <c r="A5" s="12" t="s">
+        <v>26</v>
+      </c>
+      <c r="B5" s="12" t="s">
         <v>378</v>
       </c>
-      <c r="E4" s="2" t="s">
+      <c r="C5" s="12" t="s">
         <v>379</v>
       </c>
-      <c r="F4" s="2" t="s">
+      <c r="D5" s="12" t="s">
         <v>380</v>
       </c>
     </row>
-    <row r="5" ht="57" spans="1:6">
-      <c r="A5" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="B5" s="3" t="s">
+    <row r="6" ht="61.5" spans="1:4">
+      <c r="A6" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="B6" s="12" t="s">
         <v>381</v>
       </c>
-      <c r="C5" s="3" t="s">
+      <c r="C6" s="12" t="s">
         <v>382</v>
       </c>
-      <c r="D5" s="3" t="s">
+      <c r="D6" s="12" t="s">
         <v>383</v>
       </c>
-      <c r="E5" s="3" t="s">
+    </row>
+    <row r="7" ht="61.5" spans="1:4">
+      <c r="A7" s="12" t="s">
+        <v>64</v>
+      </c>
+      <c r="B7" s="12" t="s">
         <v>384</v>
       </c>
-      <c r="F5" s="3" t="s">
+      <c r="C7" s="12" t="s">
         <v>385</v>
       </c>
-    </row>
-    <row r="6" ht="57" spans="1:6">
-      <c r="A6" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="B6" s="3" t="s">
+      <c r="D7" s="12" t="s">
         <v>386</v>
       </c>
-      <c r="C6" s="3" t="s">
-        <v>382</v>
-      </c>
-      <c r="D6" s="3" t="s">
+    </row>
+    <row r="8" ht="76.9" spans="1:4">
+      <c r="A8" s="12" t="s">
+        <v>68</v>
+      </c>
+      <c r="B8" s="12" t="s">
         <v>387</v>
       </c>
-      <c r="E6" s="3" t="s">
+      <c r="C8" s="12" t="s">
         <v>388</v>
       </c>
-      <c r="F6" s="3" t="s">
-        <v>385</v>
-      </c>
-    </row>
-    <row r="7" ht="57" spans="1:6">
-      <c r="A7" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="B7" s="3" t="s">
+      <c r="D8" s="12" t="s">
         <v>389</v>
       </c>
-      <c r="C7" s="3" t="s">
-        <v>382</v>
-      </c>
-      <c r="D7" s="3" t="s">
+    </row>
+    <row r="9" ht="107.65" spans="1:4">
+      <c r="A9" s="12" t="s">
+        <v>72</v>
+      </c>
+      <c r="B9" s="12" t="s">
         <v>390</v>
       </c>
-      <c r="E7" s="3" t="s">
+      <c r="C9" s="12" t="s">
         <v>391</v>
       </c>
-      <c r="F7" s="3" t="s">
-        <v>385</v>
-      </c>
-    </row>
-    <row r="8" ht="71.25" spans="1:6">
-      <c r="A8" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="B8" s="3" t="s">
+      <c r="D9" s="12" t="s">
         <v>392</v>
       </c>
-      <c r="C8" s="3" t="s">
-        <v>382</v>
-      </c>
-      <c r="D8" s="3" t="s">
+    </row>
+    <row r="10" ht="46.15" spans="1:4">
+      <c r="A10" s="12" t="s">
+        <v>76</v>
+      </c>
+      <c r="B10" s="12" t="s">
         <v>393</v>
       </c>
-      <c r="E8" s="3" t="s">
+      <c r="C10" s="12" t="s">
         <v>394</v>
       </c>
-      <c r="F8" s="3" t="s">
-        <v>385</v>
-      </c>
-    </row>
-    <row r="9" ht="99.75" spans="1:6">
-      <c r="A9" s="3" t="s">
-        <v>72</v>
-      </c>
-      <c r="B9" s="3" t="s">
+      <c r="D10" s="12" t="s">
         <v>395</v>
       </c>
-      <c r="C9" s="3" t="s">
-        <v>382</v>
-      </c>
-      <c r="D9" s="3" t="s">
+    </row>
+    <row r="11" ht="46.15" spans="1:4">
+      <c r="A11" s="12" t="s">
+        <v>80</v>
+      </c>
+      <c r="B11" s="12" t="s">
         <v>396</v>
       </c>
-      <c r="E9" s="3" t="s">
+      <c r="C11" s="12" t="s">
         <v>397</v>
       </c>
-      <c r="F9" s="3" t="s">
-        <v>385</v>
-      </c>
-    </row>
-    <row r="10" ht="42.75" spans="1:6">
-      <c r="A10" s="3" t="s">
-        <v>76</v>
-      </c>
-      <c r="B10" s="3" t="s">
+      <c r="D11" s="12" t="s">
         <v>398</v>
       </c>
-      <c r="C10" s="3" t="s">
-        <v>382</v>
-      </c>
-      <c r="D10" s="3" t="s">
-        <v>399</v>
-      </c>
-      <c r="E10" s="3" t="s">
-        <v>400</v>
-      </c>
-      <c r="F10" s="3" t="s">
-        <v>401</v>
-      </c>
-    </row>
-    <row r="11" ht="42.75" spans="1:6">
-      <c r="A11" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="B11" s="3" t="s">
-        <v>402</v>
-      </c>
-      <c r="C11" s="3" t="s">
-        <v>382</v>
-      </c>
-      <c r="D11" s="3" t="s">
-        <v>403</v>
-      </c>
-      <c r="E11" s="3" t="s">
-        <v>404</v>
-      </c>
-      <c r="F11" s="3" t="s">
-        <v>405</v>
-      </c>
     </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A4:F11" etc:filterBottomFollowUsedRange="0">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A4:D11" etc:filterBottomFollowUsedRange="0">
     <extLst/>
   </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -4380,123 +4731,12 @@
 <file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:C12"/>
-  <sheetFormatPr defaultColWidth="11" defaultRowHeight="14.25" outlineLevelCol="2"/>
-  <cols>
-    <col min="1" max="3" width="35.7079646017699" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="18" spans="1:1">
-      <c r="A1" s="1" t="s">
-        <v>406</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3">
-      <c r="A4" s="2" t="s">
-        <v>407</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>408</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>350</v>
-      </c>
-    </row>
-    <row r="5" ht="57" spans="1:3">
-      <c r="A5" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="B5" s="3" t="s">
-        <v>409</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>410</v>
-      </c>
-    </row>
-    <row r="6" ht="42.75" spans="1:3">
-      <c r="A6" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="B6" s="3" t="s">
-        <v>411</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>412</v>
-      </c>
-    </row>
-    <row r="7" ht="71.25" spans="1:3">
-      <c r="A7" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>413</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>414</v>
-      </c>
-    </row>
-    <row r="8" ht="71.25" spans="1:3">
-      <c r="A8" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="B8" s="3" t="s">
-        <v>415</v>
-      </c>
-      <c r="C8" s="3" t="s">
-        <v>416</v>
-      </c>
-    </row>
-    <row r="9" ht="71.25" spans="1:3">
-      <c r="A9" s="3" t="s">
-        <v>417</v>
-      </c>
-      <c r="B9" s="3" t="s">
-        <v>418</v>
-      </c>
-      <c r="C9" s="3" t="s">
-        <v>419</v>
-      </c>
-    </row>
-    <row r="10" ht="71.25" spans="1:3">
-      <c r="A10" s="3" t="s">
-        <v>417</v>
-      </c>
-      <c r="B10" s="3" t="s">
-        <v>420</v>
-      </c>
-      <c r="C10" s="3" t="s">
-        <v>421</v>
-      </c>
-    </row>
-    <row r="11" ht="71.25" spans="1:3">
-      <c r="A11" s="3" t="s">
-        <v>417</v>
-      </c>
-      <c r="B11" s="3" t="s">
-        <v>422</v>
-      </c>
-      <c r="C11" s="3" t="s">
-        <v>423</v>
-      </c>
-    </row>
-    <row r="12" ht="57" spans="1:3">
-      <c r="A12" s="3" t="s">
-        <v>417</v>
-      </c>
-      <c r="B12" s="3" t="s">
-        <v>424</v>
-      </c>
-      <c r="C12" s="3" t="s">
-        <v>425</v>
-      </c>
-    </row>
-  </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A4:C12" etc:filterBottomFollowUsedRange="0">
-    <extLst/>
-  </autoFilter>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultColWidth="9.02654867256637" defaultRowHeight="14.25"/>
+  <sheetData/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -4515,7 +4755,7 @@
       </c>
     </row>
     <row r="2" ht="26.25" spans="1:1">
-      <c r="A2" s="4" t="s">
+      <c r="A2" s="24" t="s">
         <v>17</v>
       </c>
     </row>
@@ -4658,6 +4898,131 @@
 <file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
+  <dimension ref="A1:C12"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.35" outlineLevelCol="2"/>
+  <cols>
+    <col min="1" max="1" width="47.2654867256637" style="5" customWidth="1"/>
+    <col min="2" max="3" width="35.7079646017699" style="5" customWidth="1"/>
+    <col min="4" max="16384" width="11" style="5"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:1">
+      <c r="A1" s="6" t="s">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="4" s="4" customFormat="1" ht="15" spans="1:3">
+      <c r="A4" s="7" t="s">
+        <v>400</v>
+      </c>
+      <c r="B4" s="7" t="s">
+        <v>401</v>
+      </c>
+      <c r="C4" s="7" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="5" ht="61.5" spans="1:3">
+      <c r="A5" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="B5" s="8" t="s">
+        <v>402</v>
+      </c>
+      <c r="C5" s="8" t="s">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="6" ht="46.15" spans="1:3">
+      <c r="A6" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="B6" s="8" t="s">
+        <v>404</v>
+      </c>
+      <c r="C6" s="8" t="s">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="7" ht="76.9" spans="1:3">
+      <c r="A7" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="B7" s="8" t="s">
+        <v>406</v>
+      </c>
+      <c r="C7" s="8" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="8" ht="92.25" spans="1:3">
+      <c r="A8" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="B8" s="8" t="s">
+        <v>408</v>
+      </c>
+      <c r="C8" s="8" t="s">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="9" ht="76.9" spans="1:3">
+      <c r="A9" s="8" t="s">
+        <v>410</v>
+      </c>
+      <c r="B9" s="8" t="s">
+        <v>411</v>
+      </c>
+      <c r="C9" s="8" t="s">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="10" ht="76.9" spans="1:3">
+      <c r="A10" s="8" t="s">
+        <v>410</v>
+      </c>
+      <c r="B10" s="8" t="s">
+        <v>413</v>
+      </c>
+      <c r="C10" s="8" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="11" ht="76.9" spans="1:3">
+      <c r="A11" s="8" t="s">
+        <v>410</v>
+      </c>
+      <c r="B11" s="8" t="s">
+        <v>415</v>
+      </c>
+      <c r="C11" s="8" t="s">
+        <v>416</v>
+      </c>
+    </row>
+    <row r="12" ht="76.9" spans="1:3">
+      <c r="A12" s="8" t="s">
+        <v>410</v>
+      </c>
+      <c r="B12" s="8" t="s">
+        <v>417</v>
+      </c>
+      <c r="C12" s="8" t="s">
+        <v>418</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A4:C12" etc:filterBottomFollowUsedRange="0">
+    <extLst/>
+  </autoFilter>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:D9"/>
   <sheetFormatPr defaultColWidth="11" defaultRowHeight="14.25" outlineLevelCol="3"/>
   <cols>
@@ -4666,35 +5031,35 @@
   <sheetData>
     <row r="1" ht="18" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>426</v>
+        <v>419</v>
       </c>
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="2" t="s">
-        <v>407</v>
+        <v>400</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>427</v>
+        <v>420</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>428</v>
+        <v>421</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>429</v>
+        <v>422</v>
       </c>
     </row>
     <row r="5" ht="28.5" spans="1:4">
       <c r="A5" s="3" t="s">
-        <v>430</v>
+        <v>423</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>431</v>
+        <v>424</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>432</v>
+        <v>425</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>433</v>
+        <v>426</v>
       </c>
     </row>
     <row r="6" ht="42.75" spans="1:4">
@@ -4702,13 +5067,13 @@
         <v>48</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>434</v>
+        <v>427</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>435</v>
+        <v>428</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>436</v>
+        <v>429</v>
       </c>
     </row>
     <row r="7" ht="42.75" spans="1:4">
@@ -4716,41 +5081,41 @@
         <v>52</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>437</v>
+        <v>430</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>438</v>
+        <v>431</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>439</v>
+        <v>432</v>
       </c>
     </row>
     <row r="8" ht="42.75" spans="1:4">
       <c r="A8" s="3" t="s">
-        <v>417</v>
+        <v>410</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>440</v>
+        <v>433</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>441</v>
+        <v>434</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>442</v>
+        <v>435</v>
       </c>
     </row>
     <row r="9" ht="28.5" spans="1:4">
       <c r="A9" s="3" t="s">
-        <v>443</v>
+        <v>436</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>444</v>
+        <v>437</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>445</v>
+        <v>438</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>446</v>
+        <v>439</v>
       </c>
     </row>
   </sheetData>
@@ -4917,7 +5282,7 @@
       </c>
     </row>
     <row r="2" ht="26.25" spans="1:1">
-      <c r="A2" s="4" t="s">
+      <c r="A2" s="24" t="s">
         <v>85</v>
       </c>
     </row>
@@ -4939,10 +5304,10 @@
       <c r="A5" s="3" t="s">
         <v>89</v>
       </c>
-      <c r="B5" s="5">
-        <v>31</v>
-      </c>
-      <c r="C5" s="9"/>
+      <c r="B5" s="25">
+        <v>31</v>
+      </c>
+      <c r="C5" s="26"/>
       <c r="D5" s="3" t="s">
         <v>90</v>
       </c>
@@ -4951,10 +5316,10 @@
       <c r="A6" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="B6" s="5">
+      <c r="B6" s="25">
         <v>28</v>
       </c>
-      <c r="C6" s="9">
+      <c r="C6" s="26">
         <v>90.3225806451613</v>
       </c>
       <c r="D6" s="3" t="s">
@@ -4965,10 +5330,10 @@
       <c r="A7" s="3" t="s">
         <v>93</v>
       </c>
-      <c r="B7" s="5">
+      <c r="B7" s="25">
         <v>25</v>
       </c>
-      <c r="C7" s="9">
+      <c r="C7" s="26">
         <v>80.6451612903226</v>
       </c>
       <c r="D7" s="3" t="s">
@@ -4979,10 +5344,10 @@
       <c r="A8" s="3" t="s">
         <v>95</v>
       </c>
-      <c r="B8" s="5">
+      <c r="B8" s="25">
         <v>26</v>
       </c>
-      <c r="C8" s="9">
+      <c r="C8" s="26">
         <v>83.8709677419355</v>
       </c>
       <c r="D8" s="3" t="s">
@@ -4993,10 +5358,10 @@
       <c r="A9" s="3" t="s">
         <v>97</v>
       </c>
-      <c r="B9" s="5">
+      <c r="B9" s="25">
         <v>16</v>
       </c>
-      <c r="C9" s="9">
+      <c r="C9" s="26">
         <v>51.6129032258064</v>
       </c>
       <c r="D9" s="3" t="s">
@@ -5007,10 +5372,10 @@
       <c r="A10" s="3" t="s">
         <v>99</v>
       </c>
-      <c r="B10" s="5">
+      <c r="B10" s="25">
         <v>23</v>
       </c>
-      <c r="C10" s="9">
+      <c r="C10" s="26">
         <v>74.1935483870968</v>
       </c>
       <c r="D10" s="3" t="s">
@@ -5021,10 +5386,10 @@
       <c r="A11" s="3" t="s">
         <v>101</v>
       </c>
-      <c r="B11" s="5">
+      <c r="B11" s="25">
         <v>16</v>
       </c>
-      <c r="C11" s="9">
+      <c r="C11" s="26">
         <v>51.6129032258064</v>
       </c>
       <c r="D11" s="3" t="s">
@@ -5035,10 +5400,10 @@
       <c r="A12" s="3" t="s">
         <v>103</v>
       </c>
-      <c r="B12" s="5">
+      <c r="B12" s="25">
         <v>24</v>
       </c>
-      <c r="C12" s="9">
+      <c r="C12" s="26">
         <v>77.4193548387097</v>
       </c>
       <c r="D12" s="3" t="s">
@@ -5049,10 +5414,10 @@
       <c r="A13" s="3" t="s">
         <v>105</v>
       </c>
-      <c r="B13" s="5">
+      <c r="B13" s="25">
         <v>20</v>
       </c>
-      <c r="C13" s="9">
+      <c r="C13" s="26">
         <v>64.5161290322581</v>
       </c>
       <c r="D13" s="3" t="s">
@@ -5063,10 +5428,10 @@
       <c r="A14" s="3" t="s">
         <v>107</v>
       </c>
-      <c r="B14" s="5">
+      <c r="B14" s="25">
         <v>22</v>
       </c>
-      <c r="C14" s="9">
+      <c r="C14" s="26">
         <v>70.9677419354839</v>
       </c>
       <c r="D14" s="3" t="s">
@@ -5077,10 +5442,10 @@
       <c r="A15" s="3" t="s">
         <v>109</v>
       </c>
-      <c r="B15" s="5">
+      <c r="B15" s="25">
         <v>27</v>
       </c>
-      <c r="C15" s="9">
+      <c r="C15" s="26">
         <v>87.0967741935484</v>
       </c>
       <c r="D15" s="3" t="s">
@@ -5091,10 +5456,10 @@
       <c r="A16" s="3" t="s">
         <v>111</v>
       </c>
-      <c r="B16" s="5">
+      <c r="B16" s="25">
         <v>22</v>
       </c>
-      <c r="C16" s="9">
+      <c r="C16" s="26">
         <v>70.9677419354838</v>
       </c>
       <c r="D16" s="3" t="s">
@@ -5105,10 +5470,10 @@
       <c r="A17" s="3" t="s">
         <v>113</v>
       </c>
-      <c r="B17" s="5">
+      <c r="B17" s="25">
         <v>23</v>
       </c>
-      <c r="C17" s="9">
+      <c r="C17" s="26">
         <v>74.1935483870967</v>
       </c>
       <c r="D17" s="3" t="s">
@@ -5119,10 +5484,10 @@
       <c r="A18" s="3" t="s">
         <v>115</v>
       </c>
-      <c r="B18" s="5">
+      <c r="B18" s="25">
         <v>13</v>
       </c>
-      <c r="C18" s="9">
+      <c r="C18" s="26">
         <v>41.9354838709677</v>
       </c>
       <c r="D18" s="3" t="s">
@@ -5133,10 +5498,10 @@
       <c r="A19" s="3" t="s">
         <v>117</v>
       </c>
-      <c r="B19" s="5">
+      <c r="B19" s="25">
         <v>27</v>
       </c>
-      <c r="C19" s="9">
+      <c r="C19" s="26">
         <v>87.0967741935483</v>
       </c>
       <c r="D19" s="3" t="s">
@@ -5157,62 +5522,63 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:B9"/>
-  <sheetFormatPr defaultColWidth="11" defaultRowHeight="14.25" outlineLevelCol="1"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.35" outlineLevelCol="1"/>
   <cols>
-    <col min="1" max="1" width="35.7079646017699" customWidth="1"/>
-    <col min="2" max="2" width="3.70796460176991" customWidth="1"/>
+    <col min="1" max="1" width="35.7079646017699" style="5" customWidth="1"/>
+    <col min="2" max="2" width="3.70796460176991" style="5" customWidth="1"/>
+    <col min="3" max="16384" width="11" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" ht="18" spans="1:1">
-      <c r="A1" s="1" t="s">
+    <row r="1" ht="15" spans="1:1">
+      <c r="A1" s="9" t="s">
         <v>119</v>
       </c>
     </row>
     <row r="4" spans="1:2">
-      <c r="A4" s="2" t="s">
+      <c r="A4" s="11" t="s">
         <v>120</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="B4" s="11" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="5" spans="1:2">
-      <c r="A5" s="3" t="s">
+    <row r="5" ht="15.4" spans="1:2">
+      <c r="A5" s="12" t="s">
         <v>121</v>
       </c>
-      <c r="B5" s="5">
+      <c r="B5" s="21">
         <v>38</v>
       </c>
     </row>
-    <row r="6" spans="1:2">
-      <c r="A6" s="3" t="s">
+    <row r="6" ht="15.4" spans="1:2">
+      <c r="A6" s="12" t="s">
         <v>122</v>
       </c>
-      <c r="B6" s="5">
+      <c r="B6" s="21">
         <v>32</v>
       </c>
     </row>
-    <row r="7" spans="1:2">
-      <c r="A7" s="3" t="s">
+    <row r="7" ht="15.4" spans="1:2">
+      <c r="A7" s="12" t="s">
         <v>123</v>
       </c>
-      <c r="B7" s="5">
+      <c r="B7" s="21">
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:2">
-      <c r="A8" s="3" t="s">
+    <row r="8" ht="15.4" spans="1:2">
+      <c r="A8" s="12" t="s">
         <v>124</v>
       </c>
-      <c r="B8" s="5">
+      <c r="B8" s="21">
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:2">
-      <c r="A9" s="3" t="s">
+    <row r="9" ht="15.4" spans="1:2">
+      <c r="A9" s="12" t="s">
         <v>89</v>
       </c>
-      <c r="B9" s="5">
+      <c r="B9" s="21">
         <v>31</v>
       </c>
     </row>
@@ -5230,340 +5596,341 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:E22"/>
-  <sheetFormatPr defaultColWidth="11" defaultRowHeight="14.25" outlineLevelCol="4"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.35" outlineLevelCol="4"/>
   <cols>
-    <col min="1" max="1" width="35.7079646017699" customWidth="1"/>
-    <col min="2" max="2" width="10.7079646017699" customWidth="1"/>
-    <col min="3" max="3" width="12.7079646017699" customWidth="1"/>
-    <col min="4" max="4" width="9.70796460176991" customWidth="1"/>
-    <col min="5" max="5" width="15.7079646017699" customWidth="1"/>
+    <col min="1" max="1" width="35.7079646017699" style="13" customWidth="1"/>
+    <col min="2" max="2" width="10.7079646017699" style="13" customWidth="1"/>
+    <col min="3" max="3" width="12.7079646017699" style="13" customWidth="1"/>
+    <col min="4" max="4" width="9.70796460176991" style="13" customWidth="1"/>
+    <col min="5" max="5" width="15.7079646017699" style="13" customWidth="1"/>
+    <col min="6" max="16384" width="11" style="13"/>
   </cols>
   <sheetData>
-    <row r="1" ht="18" spans="1:1">
-      <c r="A1" s="1" t="s">
+    <row r="1" ht="15" spans="1:1">
+      <c r="A1" s="19" t="s">
         <v>125</v>
       </c>
     </row>
-    <row r="4" spans="1:5">
-      <c r="A4" s="2" t="s">
+    <row r="4" ht="30" spans="1:5">
+      <c r="A4" s="7" t="s">
         <v>126</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="B4" s="7" t="s">
         <v>127</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="C4" s="7" t="s">
         <v>128</v>
       </c>
-      <c r="D4" s="2" t="s">
+      <c r="D4" s="7" t="s">
         <v>129</v>
       </c>
-      <c r="E4" s="2" t="s">
+      <c r="E4" s="7" t="s">
         <v>130</v>
       </c>
     </row>
-    <row r="5" spans="1:5">
-      <c r="A5" s="3" t="s">
+    <row r="5" ht="15.4" spans="1:5">
+      <c r="A5" s="14" t="s">
         <v>131</v>
       </c>
-      <c r="B5" s="5">
-        <v>31</v>
-      </c>
-      <c r="C5" s="5">
-        <v>31</v>
-      </c>
-      <c r="D5" s="5">
+      <c r="B5" s="15">
+        <v>31</v>
+      </c>
+      <c r="C5" s="15">
+        <v>31</v>
+      </c>
+      <c r="D5" s="15">
         <v>0</v>
       </c>
-      <c r="E5" s="9">
+      <c r="E5" s="23">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:5">
-      <c r="A6" s="3" t="s">
+    <row r="6" ht="15.4" spans="1:5">
+      <c r="A6" s="14" t="s">
         <v>132</v>
       </c>
-      <c r="B6" s="5">
-        <v>31</v>
-      </c>
-      <c r="C6" s="5">
-        <v>31</v>
-      </c>
-      <c r="D6" s="5">
+      <c r="B6" s="15">
+        <v>31</v>
+      </c>
+      <c r="C6" s="15">
+        <v>31</v>
+      </c>
+      <c r="D6" s="15">
         <v>0</v>
       </c>
-      <c r="E6" s="9">
+      <c r="E6" s="23">
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:5">
-      <c r="A7" s="3" t="s">
+    <row r="7" ht="15.4" spans="1:5">
+      <c r="A7" s="14" t="s">
         <v>133</v>
       </c>
-      <c r="B7" s="5">
-        <v>31</v>
-      </c>
-      <c r="C7" s="5">
-        <v>31</v>
-      </c>
-      <c r="D7" s="5">
+      <c r="B7" s="15">
+        <v>31</v>
+      </c>
+      <c r="C7" s="15">
+        <v>31</v>
+      </c>
+      <c r="D7" s="15">
         <v>0</v>
       </c>
-      <c r="E7" s="9">
+      <c r="E7" s="23">
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:5">
-      <c r="A8" s="3" t="s">
+    <row r="8" ht="15.4" spans="1:5">
+      <c r="A8" s="14" t="s">
         <v>134</v>
       </c>
-      <c r="B8" s="5">
-        <v>31</v>
-      </c>
-      <c r="C8" s="5">
-        <v>31</v>
-      </c>
-      <c r="D8" s="5">
+      <c r="B8" s="15">
+        <v>31</v>
+      </c>
+      <c r="C8" s="15">
+        <v>31</v>
+      </c>
+      <c r="D8" s="15">
         <v>0</v>
       </c>
-      <c r="E8" s="9">
+      <c r="E8" s="23">
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:5">
-      <c r="A9" s="3" t="s">
+    <row r="9" ht="15.4" spans="1:5">
+      <c r="A9" s="14" t="s">
         <v>135</v>
       </c>
-      <c r="B9" s="5">
-        <v>31</v>
-      </c>
-      <c r="C9" s="5">
-        <v>31</v>
-      </c>
-      <c r="D9" s="5">
+      <c r="B9" s="15">
+        <v>31</v>
+      </c>
+      <c r="C9" s="15">
+        <v>31</v>
+      </c>
+      <c r="D9" s="15">
         <v>0</v>
       </c>
-      <c r="E9" s="9">
+      <c r="E9" s="23">
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:5">
-      <c r="A10" s="3" t="s">
+    <row r="10" ht="15.4" spans="1:5">
+      <c r="A10" s="14" t="s">
         <v>136</v>
       </c>
-      <c r="B10" s="5">
-        <v>31</v>
-      </c>
-      <c r="C10" s="5">
-        <v>31</v>
-      </c>
-      <c r="D10" s="5">
+      <c r="B10" s="15">
+        <v>31</v>
+      </c>
+      <c r="C10" s="15">
+        <v>31</v>
+      </c>
+      <c r="D10" s="15">
         <v>0</v>
       </c>
-      <c r="E10" s="9">
+      <c r="E10" s="23">
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:5">
-      <c r="A11" s="3" t="s">
+    <row r="11" ht="15.4" spans="1:5">
+      <c r="A11" s="14" t="s">
         <v>137</v>
       </c>
-      <c r="B11" s="5">
-        <v>31</v>
-      </c>
-      <c r="C11" s="5">
-        <v>31</v>
-      </c>
-      <c r="D11" s="5">
+      <c r="B11" s="15">
+        <v>31</v>
+      </c>
+      <c r="C11" s="15">
+        <v>31</v>
+      </c>
+      <c r="D11" s="15">
         <v>0</v>
       </c>
-      <c r="E11" s="9">
+      <c r="E11" s="23">
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:5">
-      <c r="A12" s="3" t="s">
+    <row r="12" ht="15.4" spans="1:5">
+      <c r="A12" s="14" t="s">
         <v>138</v>
       </c>
-      <c r="B12" s="5">
-        <v>31</v>
-      </c>
-      <c r="C12" s="5">
-        <v>31</v>
-      </c>
-      <c r="D12" s="5">
+      <c r="B12" s="15">
+        <v>31</v>
+      </c>
+      <c r="C12" s="15">
+        <v>31</v>
+      </c>
+      <c r="D12" s="15">
         <v>0</v>
       </c>
-      <c r="E12" s="9">
+      <c r="E12" s="23">
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:5">
-      <c r="A13" s="3" t="s">
+    <row r="13" ht="15.4" spans="1:5">
+      <c r="A13" s="14" t="s">
         <v>139</v>
       </c>
-      <c r="B13" s="5">
-        <v>31</v>
-      </c>
-      <c r="C13" s="5">
+      <c r="B13" s="15">
+        <v>31</v>
+      </c>
+      <c r="C13" s="15">
         <v>26</v>
       </c>
-      <c r="D13" s="5">
+      <c r="D13" s="15">
         <v>5</v>
       </c>
-      <c r="E13" s="9">
+      <c r="E13" s="23">
         <v>16.1290322580645</v>
       </c>
     </row>
-    <row r="14" spans="1:5">
-      <c r="A14" s="3" t="s">
+    <row r="14" ht="15.4" spans="1:5">
+      <c r="A14" s="14" t="s">
         <v>140</v>
       </c>
-      <c r="B14" s="5">
-        <v>31</v>
-      </c>
-      <c r="C14" s="5">
-        <v>31</v>
-      </c>
-      <c r="D14" s="5">
+      <c r="B14" s="15">
+        <v>31</v>
+      </c>
+      <c r="C14" s="15">
+        <v>31</v>
+      </c>
+      <c r="D14" s="15">
         <v>0</v>
       </c>
-      <c r="E14" s="9">
+      <c r="E14" s="23">
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:5">
-      <c r="A15" s="3" t="s">
+    <row r="15" ht="15.4" spans="1:5">
+      <c r="A15" s="14" t="s">
         <v>141</v>
       </c>
-      <c r="B15" s="5">
-        <v>31</v>
-      </c>
-      <c r="C15" s="5">
-        <v>31</v>
-      </c>
-      <c r="D15" s="5">
+      <c r="B15" s="15">
+        <v>31</v>
+      </c>
+      <c r="C15" s="15">
+        <v>31</v>
+      </c>
+      <c r="D15" s="15">
         <v>0</v>
       </c>
-      <c r="E15" s="9">
+      <c r="E15" s="23">
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:5">
-      <c r="A16" s="3" t="s">
+    <row r="16" ht="15.4" spans="1:5">
+      <c r="A16" s="14" t="s">
         <v>142</v>
       </c>
-      <c r="B16" s="5">
-        <v>31</v>
-      </c>
-      <c r="C16" s="5">
-        <v>31</v>
-      </c>
-      <c r="D16" s="5">
+      <c r="B16" s="15">
+        <v>31</v>
+      </c>
+      <c r="C16" s="15">
+        <v>31</v>
+      </c>
+      <c r="D16" s="15">
         <v>0</v>
       </c>
-      <c r="E16" s="9">
+      <c r="E16" s="23">
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:5">
-      <c r="A17" s="3" t="s">
+    <row r="17" ht="15.4" spans="1:5">
+      <c r="A17" s="14" t="s">
         <v>143</v>
       </c>
-      <c r="B17" s="5">
-        <v>31</v>
-      </c>
-      <c r="C17" s="5">
-        <v>31</v>
-      </c>
-      <c r="D17" s="5">
+      <c r="B17" s="15">
+        <v>31</v>
+      </c>
+      <c r="C17" s="15">
+        <v>31</v>
+      </c>
+      <c r="D17" s="15">
         <v>0</v>
       </c>
-      <c r="E17" s="9">
+      <c r="E17" s="23">
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:5">
-      <c r="A18" s="3" t="s">
+    <row r="18" ht="15.4" spans="1:5">
+      <c r="A18" s="14" t="s">
         <v>144</v>
       </c>
-      <c r="B18" s="5">
-        <v>31</v>
-      </c>
-      <c r="C18" s="5">
-        <v>31</v>
-      </c>
-      <c r="D18" s="5">
+      <c r="B18" s="15">
+        <v>31</v>
+      </c>
+      <c r="C18" s="15">
+        <v>31</v>
+      </c>
+      <c r="D18" s="15">
         <v>0</v>
       </c>
-      <c r="E18" s="9">
+      <c r="E18" s="23">
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:5">
-      <c r="A19" s="3" t="s">
+    <row r="19" ht="15.4" spans="1:5">
+      <c r="A19" s="14" t="s">
         <v>145</v>
       </c>
-      <c r="B19" s="5">
-        <v>31</v>
-      </c>
-      <c r="C19" s="5">
-        <v>31</v>
-      </c>
-      <c r="D19" s="5">
+      <c r="B19" s="15">
+        <v>31</v>
+      </c>
+      <c r="C19" s="15">
+        <v>31</v>
+      </c>
+      <c r="D19" s="15">
         <v>0</v>
       </c>
-      <c r="E19" s="9">
+      <c r="E19" s="23">
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:5">
-      <c r="A20" s="3" t="s">
+    <row r="20" ht="15.4" spans="1:5">
+      <c r="A20" s="14" t="s">
         <v>146</v>
       </c>
-      <c r="B20" s="5">
-        <v>31</v>
-      </c>
-      <c r="C20" s="5">
+      <c r="B20" s="15">
+        <v>31</v>
+      </c>
+      <c r="C20" s="15">
         <v>9</v>
       </c>
-      <c r="D20" s="5">
+      <c r="D20" s="15">
         <v>22</v>
       </c>
-      <c r="E20" s="9">
+      <c r="E20" s="23">
         <v>70.9677419354839</v>
       </c>
     </row>
-    <row r="21" spans="1:5">
-      <c r="A21" s="3" t="s">
+    <row r="21" ht="15.4" spans="1:5">
+      <c r="A21" s="14" t="s">
         <v>147</v>
       </c>
-      <c r="B21" s="5">
-        <v>31</v>
-      </c>
-      <c r="C21" s="5">
-        <v>31</v>
-      </c>
-      <c r="D21" s="5">
+      <c r="B21" s="15">
+        <v>31</v>
+      </c>
+      <c r="C21" s="15">
+        <v>31</v>
+      </c>
+      <c r="D21" s="15">
         <v>0</v>
       </c>
-      <c r="E21" s="9">
+      <c r="E21" s="23">
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:5">
-      <c r="A22" s="3" t="s">
+    <row r="22" ht="15.4" spans="1:5">
+      <c r="A22" s="14" t="s">
         <v>148</v>
       </c>
-      <c r="B22" s="5">
-        <v>31</v>
-      </c>
-      <c r="C22" s="5">
+      <c r="B22" s="15">
+        <v>31</v>
+      </c>
+      <c r="C22" s="15">
         <v>12</v>
       </c>
-      <c r="D22" s="5">
+      <c r="D22" s="15">
         <v>19</v>
       </c>
-      <c r="E22" s="9">
+      <c r="E22" s="23">
         <v>61.2903225806452</v>
       </c>
     </row>
@@ -5581,409 +5948,410 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:C39"/>
-  <sheetFormatPr defaultColWidth="11" defaultRowHeight="14.25" outlineLevelCol="2"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.35" outlineLevelCol="2"/>
   <cols>
-    <col min="1" max="3" width="35.7079646017699" customWidth="1"/>
+    <col min="1" max="3" width="35.7079646017699" style="13" customWidth="1"/>
+    <col min="4" max="16384" width="11" style="13"/>
   </cols>
   <sheetData>
-    <row r="1" ht="18" spans="1:1">
-      <c r="A1" s="1" t="s">
+    <row r="1" ht="15" spans="1:1">
+      <c r="A1" s="19" t="s">
         <v>149</v>
       </c>
     </row>
-    <row r="4" spans="1:3">
-      <c r="A4" s="2" t="s">
+    <row r="4" ht="15" spans="1:3">
+      <c r="A4" s="7" t="s">
         <v>150</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="B4" s="7" t="s">
         <v>151</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="C4" s="7" t="s">
         <v>152</v>
       </c>
     </row>
-    <row r="5" spans="1:3">
-      <c r="A5" s="3" t="s">
+    <row r="5" ht="15.4" spans="1:3">
+      <c r="A5" s="14" t="s">
         <v>153</v>
       </c>
-      <c r="B5" s="3" t="s">
+      <c r="B5" s="14" t="s">
         <v>154</v>
       </c>
-      <c r="C5" s="3" t="s">
+      <c r="C5" s="14" t="s">
         <v>153</v>
       </c>
     </row>
-    <row r="6" spans="1:3">
-      <c r="A6" s="3" t="s">
+    <row r="6" ht="15.4" spans="1:3">
+      <c r="A6" s="14" t="s">
         <v>155</v>
       </c>
-      <c r="B6" s="3" t="s">
+      <c r="B6" s="14" t="s">
         <v>156</v>
       </c>
-      <c r="C6" s="3" t="s">
+      <c r="C6" s="14" t="s">
         <v>155</v>
       </c>
     </row>
-    <row r="7" spans="1:3">
-      <c r="A7" s="3" t="s">
+    <row r="7" ht="15.4" spans="1:3">
+      <c r="A7" s="14" t="s">
         <v>157</v>
       </c>
-      <c r="B7" s="3" t="s">
+      <c r="B7" s="14" t="s">
         <v>158</v>
       </c>
-      <c r="C7" s="3" t="s">
+      <c r="C7" s="14" t="s">
         <v>157</v>
       </c>
     </row>
-    <row r="8" spans="1:3">
-      <c r="A8" s="3" t="s">
+    <row r="8" ht="15.4" spans="1:3">
+      <c r="A8" s="14" t="s">
         <v>159</v>
       </c>
-      <c r="B8" s="3" t="s">
+      <c r="B8" s="14" t="s">
         <v>160</v>
       </c>
-      <c r="C8" s="3" t="s">
+      <c r="C8" s="14" t="s">
         <v>159</v>
       </c>
     </row>
-    <row r="9" spans="1:3">
-      <c r="A9" s="3" t="s">
+    <row r="9" ht="15.4" spans="1:3">
+      <c r="A9" s="14" t="s">
         <v>161</v>
       </c>
-      <c r="B9" s="3" t="s">
+      <c r="B9" s="14" t="s">
         <v>162</v>
       </c>
-      <c r="C9" s="3" t="s">
+      <c r="C9" s="14" t="s">
         <v>161</v>
       </c>
     </row>
-    <row r="10" spans="1:3">
-      <c r="A10" s="3" t="s">
+    <row r="10" ht="15.4" spans="1:3">
+      <c r="A10" s="14" t="s">
         <v>163</v>
       </c>
-      <c r="B10" s="3" t="s">
+      <c r="B10" s="14" t="s">
         <v>164</v>
       </c>
-      <c r="C10" s="3" t="s">
+      <c r="C10" s="14" t="s">
         <v>163</v>
       </c>
     </row>
-    <row r="11" spans="1:3">
-      <c r="A11" s="3" t="s">
+    <row r="11" ht="15.4" spans="1:3">
+      <c r="A11" s="14" t="s">
         <v>165</v>
       </c>
-      <c r="B11" s="3" t="s">
+      <c r="B11" s="14" t="s">
         <v>166</v>
       </c>
-      <c r="C11" s="3" t="s">
+      <c r="C11" s="14" t="s">
         <v>165</v>
       </c>
     </row>
-    <row r="12" spans="1:3">
-      <c r="A12" s="3" t="s">
+    <row r="12" ht="15.4" spans="1:3">
+      <c r="A12" s="14" t="s">
         <v>167</v>
       </c>
-      <c r="B12" s="3" t="s">
+      <c r="B12" s="14" t="s">
         <v>168</v>
       </c>
-      <c r="C12" s="3" t="s">
+      <c r="C12" s="14" t="s">
         <v>167</v>
       </c>
     </row>
-    <row r="13" spans="1:3">
-      <c r="A13" s="3" t="s">
+    <row r="13" ht="15.4" spans="1:3">
+      <c r="A13" s="14" t="s">
         <v>169</v>
       </c>
-      <c r="B13" s="3" t="s">
+      <c r="B13" s="14" t="s">
         <v>170</v>
       </c>
-      <c r="C13" s="3" t="s">
+      <c r="C13" s="14" t="s">
         <v>169</v>
       </c>
     </row>
-    <row r="14" spans="1:3">
-      <c r="A14" s="3" t="s">
+    <row r="14" ht="15.4" spans="1:3">
+      <c r="A14" s="14" t="s">
         <v>171</v>
       </c>
-      <c r="B14" s="3" t="s">
+      <c r="B14" s="14" t="s">
         <v>172</v>
       </c>
-      <c r="C14" s="3" t="s">
+      <c r="C14" s="14" t="s">
         <v>171</v>
       </c>
     </row>
-    <row r="15" spans="1:3">
-      <c r="A15" s="3" t="s">
+    <row r="15" ht="15.4" spans="1:3">
+      <c r="A15" s="14" t="s">
         <v>173</v>
       </c>
-      <c r="B15" s="3" t="s">
+      <c r="B15" s="14" t="s">
         <v>174</v>
       </c>
-      <c r="C15" s="3" t="s">
+      <c r="C15" s="14" t="s">
         <v>173</v>
       </c>
     </row>
-    <row r="16" spans="1:3">
-      <c r="A16" s="3" t="s">
+    <row r="16" ht="15.4" spans="1:3">
+      <c r="A16" s="14" t="s">
         <v>175</v>
       </c>
-      <c r="B16" s="3" t="s">
+      <c r="B16" s="14" t="s">
         <v>176</v>
       </c>
-      <c r="C16" s="3" t="s">
+      <c r="C16" s="14" t="s">
         <v>175</v>
       </c>
     </row>
-    <row r="17" spans="1:3">
-      <c r="A17" s="3" t="s">
+    <row r="17" ht="15.4" spans="1:3">
+      <c r="A17" s="14" t="s">
         <v>177</v>
       </c>
-      <c r="B17" s="3" t="s">
+      <c r="B17" s="14" t="s">
         <v>178</v>
       </c>
-      <c r="C17" s="3" t="s">
+      <c r="C17" s="14" t="s">
         <v>177</v>
       </c>
     </row>
-    <row r="18" spans="1:3">
-      <c r="A18" s="3" t="s">
+    <row r="18" ht="15.4" spans="1:3">
+      <c r="A18" s="14" t="s">
         <v>179</v>
       </c>
-      <c r="B18" s="3" t="s">
+      <c r="B18" s="14" t="s">
         <v>180</v>
       </c>
-      <c r="C18" s="3" t="s">
+      <c r="C18" s="14" t="s">
         <v>179</v>
       </c>
     </row>
-    <row r="19" spans="1:3">
-      <c r="A19" s="3" t="s">
+    <row r="19" ht="15.4" spans="1:3">
+      <c r="A19" s="14" t="s">
         <v>181</v>
       </c>
-      <c r="B19" s="3" t="s">
+      <c r="B19" s="14" t="s">
         <v>182</v>
       </c>
-      <c r="C19" s="3" t="s">
+      <c r="C19" s="14" t="s">
         <v>181</v>
       </c>
     </row>
-    <row r="20" spans="1:3">
-      <c r="A20" s="3" t="s">
+    <row r="20" ht="15.4" spans="1:3">
+      <c r="A20" s="14" t="s">
         <v>183</v>
       </c>
-      <c r="B20" s="3" t="s">
+      <c r="B20" s="14" t="s">
         <v>184</v>
       </c>
-      <c r="C20" s="3" t="s">
+      <c r="C20" s="14" t="s">
         <v>183</v>
       </c>
     </row>
-    <row r="21" spans="1:3">
-      <c r="A21" s="3" t="s">
+    <row r="21" ht="15.4" spans="1:3">
+      <c r="A21" s="14" t="s">
         <v>185</v>
       </c>
-      <c r="B21" s="3" t="s">
+      <c r="B21" s="14" t="s">
         <v>186</v>
       </c>
-      <c r="C21" s="3" t="s">
+      <c r="C21" s="14" t="s">
         <v>185</v>
       </c>
     </row>
-    <row r="22" ht="28.5" spans="1:3">
-      <c r="A22" s="3" t="s">
+    <row r="22" ht="30.75" spans="1:3">
+      <c r="A22" s="14" t="s">
         <v>187</v>
       </c>
-      <c r="B22" s="3" t="s">
+      <c r="B22" s="14" t="s">
         <v>188</v>
       </c>
-      <c r="C22" s="3" t="s">
+      <c r="C22" s="14" t="s">
         <v>131</v>
       </c>
     </row>
-    <row r="23" spans="1:3">
-      <c r="A23" s="3" t="s">
+    <row r="23" ht="15.4" spans="1:3">
+      <c r="A23" s="14" t="s">
         <v>189</v>
       </c>
-      <c r="B23" s="3" t="s">
+      <c r="B23" s="14" t="s">
         <v>190</v>
       </c>
-      <c r="C23" s="3" t="s">
+      <c r="C23" s="14" t="s">
         <v>132</v>
       </c>
     </row>
-    <row r="24" ht="57" spans="1:3">
-      <c r="A24" s="3" t="s">
+    <row r="24" ht="61.5" spans="1:3">
+      <c r="A24" s="14" t="s">
         <v>191</v>
       </c>
-      <c r="B24" s="3" t="s">
+      <c r="B24" s="14" t="s">
         <v>192</v>
       </c>
-      <c r="C24" s="3" t="s">
+      <c r="C24" s="14" t="s">
         <v>133</v>
       </c>
     </row>
-    <row r="25" ht="57" spans="1:3">
-      <c r="A25" s="3" t="s">
+    <row r="25" ht="76.9" spans="1:3">
+      <c r="A25" s="14" t="s">
         <v>193</v>
       </c>
-      <c r="B25" s="3" t="s">
+      <c r="B25" s="14" t="s">
         <v>194</v>
       </c>
-      <c r="C25" s="3" t="s">
+      <c r="C25" s="14" t="s">
         <v>134</v>
       </c>
     </row>
-    <row r="26" ht="42.75" spans="1:3">
-      <c r="A26" s="3" t="s">
+    <row r="26" ht="46.15" spans="1:3">
+      <c r="A26" s="14" t="s">
         <v>195</v>
       </c>
-      <c r="B26" s="3" t="s">
+      <c r="B26" s="14" t="s">
         <v>196</v>
       </c>
-      <c r="C26" s="3" t="s">
+      <c r="C26" s="14" t="s">
         <v>135</v>
       </c>
     </row>
-    <row r="27" ht="42.75" spans="1:3">
-      <c r="A27" s="3" t="s">
+    <row r="27" ht="61.5" spans="1:3">
+      <c r="A27" s="14" t="s">
         <v>197</v>
       </c>
-      <c r="B27" s="3" t="s">
+      <c r="B27" s="14" t="s">
         <v>198</v>
       </c>
-      <c r="C27" s="3" t="s">
+      <c r="C27" s="14" t="s">
         <v>136</v>
       </c>
     </row>
-    <row r="28" ht="28.5" spans="1:3">
-      <c r="A28" s="3" t="s">
+    <row r="28" ht="30.75" spans="1:3">
+      <c r="A28" s="14" t="s">
         <v>199</v>
       </c>
-      <c r="B28" s="3" t="s">
+      <c r="B28" s="14" t="s">
         <v>200</v>
       </c>
-      <c r="C28" s="3" t="s">
+      <c r="C28" s="14" t="s">
         <v>137</v>
       </c>
     </row>
-    <row r="29" ht="28.5" spans="1:3">
-      <c r="A29" s="3" t="s">
+    <row r="29" ht="30.75" spans="1:3">
+      <c r="A29" s="14" t="s">
         <v>201</v>
       </c>
-      <c r="B29" s="3" t="s">
+      <c r="B29" s="14" t="s">
         <v>202</v>
       </c>
-      <c r="C29" s="3" t="s">
+      <c r="C29" s="14" t="s">
         <v>138</v>
       </c>
     </row>
-    <row r="30" ht="42.75" spans="1:3">
-      <c r="A30" s="3" t="s">
+    <row r="30" ht="46.15" spans="1:3">
+      <c r="A30" s="14" t="s">
         <v>203</v>
       </c>
-      <c r="B30" s="3" t="s">
+      <c r="B30" s="14" t="s">
         <v>204</v>
       </c>
-      <c r="C30" s="3" t="s">
+      <c r="C30" s="14" t="s">
         <v>139</v>
       </c>
     </row>
-    <row r="31" ht="28.5" spans="1:3">
-      <c r="A31" s="3" t="s">
+    <row r="31" ht="30.75" spans="1:3">
+      <c r="A31" s="14" t="s">
         <v>205</v>
       </c>
-      <c r="B31" s="3" t="s">
+      <c r="B31" s="14" t="s">
         <v>206</v>
       </c>
-      <c r="C31" s="3" t="s">
+      <c r="C31" s="14" t="s">
         <v>140</v>
       </c>
     </row>
-    <row r="32" ht="28.5" spans="1:3">
-      <c r="A32" s="3" t="s">
+    <row r="32" ht="30.75" spans="1:3">
+      <c r="A32" s="14" t="s">
         <v>207</v>
       </c>
-      <c r="B32" s="3" t="s">
+      <c r="B32" s="14" t="s">
         <v>208</v>
       </c>
-      <c r="C32" s="3" t="s">
+      <c r="C32" s="14" t="s">
         <v>141</v>
       </c>
     </row>
-    <row r="33" ht="42.75" spans="1:3">
-      <c r="A33" s="3" t="s">
+    <row r="33" ht="46.15" spans="1:3">
+      <c r="A33" s="14" t="s">
         <v>209</v>
       </c>
-      <c r="B33" s="3" t="s">
+      <c r="B33" s="14" t="s">
         <v>210</v>
       </c>
-      <c r="C33" s="3" t="s">
+      <c r="C33" s="14" t="s">
         <v>142</v>
       </c>
     </row>
-    <row r="34" ht="42.75" spans="1:3">
-      <c r="A34" s="3" t="s">
+    <row r="34" ht="46.15" spans="1:3">
+      <c r="A34" s="14" t="s">
         <v>211</v>
       </c>
-      <c r="B34" s="3" t="s">
+      <c r="B34" s="14" t="s">
         <v>212</v>
       </c>
-      <c r="C34" s="3" t="s">
+      <c r="C34" s="14" t="s">
         <v>143</v>
       </c>
     </row>
-    <row r="35" ht="57" spans="1:3">
-      <c r="A35" s="3" t="s">
+    <row r="35" ht="61.5" spans="1:3">
+      <c r="A35" s="14" t="s">
         <v>213</v>
       </c>
-      <c r="B35" s="3" t="s">
+      <c r="B35" s="14" t="s">
         <v>214</v>
       </c>
-      <c r="C35" s="3" t="s">
+      <c r="C35" s="14" t="s">
         <v>144</v>
       </c>
     </row>
-    <row r="36" ht="57" spans="1:3">
-      <c r="A36" s="3" t="s">
+    <row r="36" ht="61.5" spans="1:3">
+      <c r="A36" s="14" t="s">
         <v>215</v>
       </c>
-      <c r="B36" s="3" t="s">
+      <c r="B36" s="14" t="s">
         <v>216</v>
       </c>
-      <c r="C36" s="3" t="s">
+      <c r="C36" s="14" t="s">
         <v>145</v>
       </c>
     </row>
-    <row r="37" ht="57" spans="1:3">
-      <c r="A37" s="3" t="s">
+    <row r="37" ht="76.9" spans="1:3">
+      <c r="A37" s="14" t="s">
         <v>217</v>
       </c>
-      <c r="B37" s="3" t="s">
+      <c r="B37" s="14" t="s">
         <v>218</v>
       </c>
-      <c r="C37" s="3" t="s">
+      <c r="C37" s="14" t="s">
         <v>146</v>
       </c>
     </row>
-    <row r="38" ht="28.5" spans="1:3">
-      <c r="A38" s="3" t="s">
+    <row r="38" ht="30.75" spans="1:3">
+      <c r="A38" s="14" t="s">
         <v>219</v>
       </c>
-      <c r="B38" s="3" t="s">
+      <c r="B38" s="14" t="s">
         <v>220</v>
       </c>
-      <c r="C38" s="3" t="s">
+      <c r="C38" s="14" t="s">
         <v>147</v>
       </c>
     </row>
-    <row r="39" ht="42.75" spans="1:3">
-      <c r="A39" s="3" t="s">
+    <row r="39" ht="46.15" spans="1:3">
+      <c r="A39" s="14" t="s">
         <v>221</v>
       </c>
-      <c r="B39" s="3" t="s">
+      <c r="B39" s="14" t="s">
         <v>222</v>
       </c>
-      <c r="C39" s="3" t="s">
+      <c r="C39" s="14" t="s">
         <v>148</v>
       </c>
     </row>
@@ -6001,1478 +6369,1479 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:H59"/>
-  <sheetFormatPr defaultColWidth="11" defaultRowHeight="14.25" outlineLevelCol="7"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.35" outlineLevelCol="7"/>
   <cols>
-    <col min="1" max="3" width="35.7079646017699" customWidth="1"/>
-    <col min="4" max="4" width="3.70796460176991" customWidth="1"/>
-    <col min="5" max="5" width="10.7079646017699" customWidth="1"/>
-    <col min="6" max="6" width="7.70796460176991" customWidth="1"/>
-    <col min="7" max="8" width="13.7079646017699" customWidth="1"/>
+    <col min="1" max="3" width="35.7079646017699" style="5" customWidth="1"/>
+    <col min="4" max="4" width="3.70796460176991" style="5" customWidth="1"/>
+    <col min="5" max="5" width="10.7079646017699" style="5" customWidth="1"/>
+    <col min="6" max="6" width="7.70796460176991" style="5" customWidth="1"/>
+    <col min="7" max="8" width="13.7079646017699" style="5" customWidth="1"/>
+    <col min="9" max="16384" width="11" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" ht="18" spans="1:1">
-      <c r="A1" s="1" t="s">
+    <row r="1" ht="15" spans="1:1">
+      <c r="A1" s="9" t="s">
         <v>223</v>
       </c>
     </row>
-    <row r="2" ht="26.25" spans="1:1">
-      <c r="A2" s="4" t="s">
+    <row r="2" ht="30.75" spans="1:1">
+      <c r="A2" s="10" t="s">
         <v>224</v>
       </c>
     </row>
-    <row r="4" spans="1:8">
-      <c r="A4" s="2" t="s">
+    <row r="4" ht="15" spans="1:8">
+      <c r="A4" s="11" t="s">
         <v>126</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="B4" s="11" t="s">
         <v>225</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="C4" s="11" t="s">
         <v>226</v>
       </c>
-      <c r="D4" s="2" t="s">
+      <c r="D4" s="11" t="s">
         <v>87</v>
       </c>
-      <c r="E4" s="2" t="s">
+      <c r="E4" s="11" t="s">
         <v>127</v>
       </c>
-      <c r="F4" s="2" t="s">
+      <c r="F4" s="11" t="s">
         <v>227</v>
       </c>
-      <c r="G4" s="2" t="s">
+      <c r="G4" s="11" t="s">
         <v>228</v>
       </c>
-      <c r="H4" s="2" t="s">
+      <c r="H4" s="11" t="s">
         <v>229</v>
       </c>
     </row>
-    <row r="5" spans="1:8">
-      <c r="A5" s="3" t="s">
+    <row r="5" ht="15.4" spans="1:8">
+      <c r="A5" s="12" t="s">
         <v>131</v>
       </c>
-      <c r="B5" s="3" t="s">
+      <c r="B5" s="12" t="s">
         <v>230</v>
       </c>
-      <c r="C5" s="3" t="s">
+      <c r="C5" s="12" t="s">
         <v>231</v>
       </c>
-      <c r="D5" s="5">
+      <c r="D5" s="21">
         <v>1</v>
       </c>
-      <c r="E5" s="5">
-        <v>31</v>
-      </c>
-      <c r="F5" s="5">
-        <v>31</v>
-      </c>
-      <c r="G5" s="9">
+      <c r="E5" s="21">
+        <v>31</v>
+      </c>
+      <c r="F5" s="21">
+        <v>31</v>
+      </c>
+      <c r="G5" s="22">
         <v>3.2258064516129</v>
       </c>
-      <c r="H5" s="9">
+      <c r="H5" s="22">
         <v>3.2258064516129</v>
       </c>
     </row>
-    <row r="6" spans="1:8">
-      <c r="A6" s="3" t="s">
+    <row r="6" ht="15.4" spans="1:8">
+      <c r="A6" s="12" t="s">
         <v>131</v>
       </c>
-      <c r="B6" s="3" t="s">
+      <c r="B6" s="12" t="s">
         <v>230</v>
       </c>
-      <c r="C6" s="3" t="s">
+      <c r="C6" s="12" t="s">
         <v>232</v>
       </c>
-      <c r="D6" s="5">
+      <c r="D6" s="21">
         <v>2</v>
       </c>
-      <c r="E6" s="5">
-        <v>31</v>
-      </c>
-      <c r="F6" s="5">
-        <v>31</v>
-      </c>
-      <c r="G6" s="9">
+      <c r="E6" s="21">
+        <v>31</v>
+      </c>
+      <c r="F6" s="21">
+        <v>31</v>
+      </c>
+      <c r="G6" s="22">
         <v>6.45161290322581</v>
       </c>
-      <c r="H6" s="9">
+      <c r="H6" s="22">
         <v>6.45161290322581</v>
       </c>
     </row>
-    <row r="7" spans="1:8">
-      <c r="A7" s="3" t="s">
+    <row r="7" ht="15.4" spans="1:8">
+      <c r="A7" s="12" t="s">
         <v>131</v>
       </c>
-      <c r="B7" s="3" t="s">
+      <c r="B7" s="12" t="s">
         <v>230</v>
       </c>
-      <c r="C7" s="3" t="s">
+      <c r="C7" s="12" t="s">
         <v>233</v>
       </c>
-      <c r="D7" s="5">
+      <c r="D7" s="21">
         <v>28</v>
       </c>
-      <c r="E7" s="5">
-        <v>31</v>
-      </c>
-      <c r="F7" s="5">
-        <v>31</v>
-      </c>
-      <c r="G7" s="9">
+      <c r="E7" s="21">
+        <v>31</v>
+      </c>
+      <c r="F7" s="21">
+        <v>31</v>
+      </c>
+      <c r="G7" s="22">
         <v>90.3225806451613</v>
       </c>
-      <c r="H7" s="9">
+      <c r="H7" s="22">
         <v>90.3225806451613</v>
       </c>
     </row>
-    <row r="8" spans="1:8">
-      <c r="A8" s="3" t="s">
+    <row r="8" ht="15.4" spans="1:8">
+      <c r="A8" s="12" t="s">
         <v>132</v>
       </c>
-      <c r="B8" s="3" t="s">
+      <c r="B8" s="12" t="s">
         <v>234</v>
       </c>
-      <c r="C8" s="3" t="s">
+      <c r="C8" s="12" t="s">
         <v>235</v>
       </c>
-      <c r="D8" s="5">
-        <v>31</v>
-      </c>
-      <c r="E8" s="5">
-        <v>31</v>
-      </c>
-      <c r="F8" s="5">
-        <v>31</v>
-      </c>
-      <c r="G8" s="9">
+      <c r="D8" s="21">
+        <v>31</v>
+      </c>
+      <c r="E8" s="21">
+        <v>31</v>
+      </c>
+      <c r="F8" s="21">
+        <v>31</v>
+      </c>
+      <c r="G8" s="22">
         <v>100</v>
       </c>
-      <c r="H8" s="9">
+      <c r="H8" s="22">
         <v>100</v>
       </c>
     </row>
-    <row r="9" spans="1:8">
-      <c r="A9" s="3" t="s">
+    <row r="9" ht="15.4" spans="1:8">
+      <c r="A9" s="12" t="s">
         <v>133</v>
       </c>
-      <c r="B9" s="3" t="s">
+      <c r="B9" s="12" t="s">
         <v>236</v>
       </c>
-      <c r="C9" s="3" t="s">
+      <c r="C9" s="12" t="s">
         <v>237</v>
       </c>
-      <c r="D9" s="5">
+      <c r="D9" s="21">
         <v>1</v>
       </c>
-      <c r="E9" s="5">
-        <v>31</v>
-      </c>
-      <c r="F9" s="5">
-        <v>31</v>
-      </c>
-      <c r="G9" s="9">
+      <c r="E9" s="21">
+        <v>31</v>
+      </c>
+      <c r="F9" s="21">
+        <v>31</v>
+      </c>
+      <c r="G9" s="22">
         <v>3.2258064516129</v>
       </c>
-      <c r="H9" s="9">
+      <c r="H9" s="22">
         <v>3.2258064516129</v>
       </c>
     </row>
-    <row r="10" spans="1:8">
-      <c r="A10" s="3" t="s">
+    <row r="10" ht="15.4" spans="1:8">
+      <c r="A10" s="12" t="s">
         <v>133</v>
       </c>
-      <c r="B10" s="3" t="s">
+      <c r="B10" s="12" t="s">
         <v>236</v>
       </c>
-      <c r="C10" s="3" t="s">
+      <c r="C10" s="12" t="s">
         <v>238</v>
       </c>
-      <c r="D10" s="5">
+      <c r="D10" s="21">
         <v>5</v>
       </c>
-      <c r="E10" s="5">
-        <v>31</v>
-      </c>
-      <c r="F10" s="5">
-        <v>31</v>
-      </c>
-      <c r="G10" s="9">
+      <c r="E10" s="21">
+        <v>31</v>
+      </c>
+      <c r="F10" s="21">
+        <v>31</v>
+      </c>
+      <c r="G10" s="22">
         <v>16.1290322580645</v>
       </c>
-      <c r="H10" s="9">
+      <c r="H10" s="22">
         <v>16.1290322580645</v>
       </c>
     </row>
-    <row r="11" spans="1:8">
-      <c r="A11" s="3" t="s">
+    <row r="11" ht="15.4" spans="1:8">
+      <c r="A11" s="12" t="s">
         <v>133</v>
       </c>
-      <c r="B11" s="3" t="s">
+      <c r="B11" s="12" t="s">
         <v>236</v>
       </c>
-      <c r="C11" s="3" t="s">
+      <c r="C11" s="12" t="s">
         <v>239</v>
       </c>
-      <c r="D11" s="5">
+      <c r="D11" s="21">
         <v>25</v>
       </c>
-      <c r="E11" s="5">
-        <v>31</v>
-      </c>
-      <c r="F11" s="5">
-        <v>31</v>
-      </c>
-      <c r="G11" s="9">
+      <c r="E11" s="21">
+        <v>31</v>
+      </c>
+      <c r="F11" s="21">
+        <v>31</v>
+      </c>
+      <c r="G11" s="22">
         <v>80.6451612903226</v>
       </c>
-      <c r="H11" s="9">
+      <c r="H11" s="22">
         <v>80.6451612903226</v>
       </c>
     </row>
-    <row r="12" spans="1:8">
-      <c r="A12" s="3" t="s">
+    <row r="12" ht="15.4" spans="1:8">
+      <c r="A12" s="12" t="s">
         <v>134</v>
       </c>
-      <c r="B12" s="3" t="s">
+      <c r="B12" s="12" t="s">
         <v>240</v>
       </c>
-      <c r="C12" s="3" t="s">
+      <c r="C12" s="12" t="s">
         <v>241</v>
       </c>
-      <c r="D12" s="5">
+      <c r="D12" s="21">
         <v>3</v>
       </c>
-      <c r="E12" s="5">
-        <v>31</v>
-      </c>
-      <c r="F12" s="5">
-        <v>31</v>
-      </c>
-      <c r="G12" s="9">
+      <c r="E12" s="21">
+        <v>31</v>
+      </c>
+      <c r="F12" s="21">
+        <v>31</v>
+      </c>
+      <c r="G12" s="22">
         <v>9.67741935483871</v>
       </c>
-      <c r="H12" s="9">
+      <c r="H12" s="22">
         <v>9.67741935483871</v>
       </c>
     </row>
-    <row r="13" spans="1:8">
-      <c r="A13" s="3" t="s">
+    <row r="13" ht="15.4" spans="1:8">
+      <c r="A13" s="12" t="s">
         <v>134</v>
       </c>
-      <c r="B13" s="3" t="s">
+      <c r="B13" s="12" t="s">
         <v>240</v>
       </c>
-      <c r="C13" s="3" t="s">
+      <c r="C13" s="12" t="s">
         <v>242</v>
       </c>
-      <c r="D13" s="5">
+      <c r="D13" s="21">
         <v>9</v>
       </c>
-      <c r="E13" s="5">
-        <v>31</v>
-      </c>
-      <c r="F13" s="5">
-        <v>31</v>
-      </c>
-      <c r="G13" s="9">
+      <c r="E13" s="21">
+        <v>31</v>
+      </c>
+      <c r="F13" s="21">
+        <v>31</v>
+      </c>
+      <c r="G13" s="22">
         <v>29.0322580645161</v>
       </c>
-      <c r="H13" s="9">
+      <c r="H13" s="22">
         <v>29.0322580645161</v>
       </c>
     </row>
-    <row r="14" spans="1:8">
-      <c r="A14" s="3" t="s">
+    <row r="14" ht="15.4" spans="1:8">
+      <c r="A14" s="12" t="s">
         <v>134</v>
       </c>
-      <c r="B14" s="3" t="s">
+      <c r="B14" s="12" t="s">
         <v>240</v>
       </c>
-      <c r="C14" s="3" t="s">
+      <c r="C14" s="12" t="s">
         <v>243</v>
       </c>
-      <c r="D14" s="5">
+      <c r="D14" s="21">
         <v>2</v>
       </c>
-      <c r="E14" s="5">
-        <v>31</v>
-      </c>
-      <c r="F14" s="5">
-        <v>31</v>
-      </c>
-      <c r="G14" s="9">
+      <c r="E14" s="21">
+        <v>31</v>
+      </c>
+      <c r="F14" s="21">
+        <v>31</v>
+      </c>
+      <c r="G14" s="22">
         <v>6.45161290322581</v>
       </c>
-      <c r="H14" s="9">
+      <c r="H14" s="22">
         <v>6.45161290322581</v>
       </c>
     </row>
-    <row r="15" spans="1:8">
-      <c r="A15" s="3" t="s">
+    <row r="15" ht="15.4" spans="1:8">
+      <c r="A15" s="12" t="s">
         <v>134</v>
       </c>
-      <c r="B15" s="3" t="s">
+      <c r="B15" s="12" t="s">
         <v>240</v>
       </c>
-      <c r="C15" s="3" t="s">
+      <c r="C15" s="12" t="s">
         <v>244</v>
       </c>
-      <c r="D15" s="5">
+      <c r="D15" s="21">
         <v>17</v>
       </c>
-      <c r="E15" s="5">
-        <v>31</v>
-      </c>
-      <c r="F15" s="5">
-        <v>31</v>
-      </c>
-      <c r="G15" s="9">
+      <c r="E15" s="21">
+        <v>31</v>
+      </c>
+      <c r="F15" s="21">
+        <v>31</v>
+      </c>
+      <c r="G15" s="22">
         <v>54.8387096774194</v>
       </c>
-      <c r="H15" s="9">
+      <c r="H15" s="22">
         <v>54.8387096774194</v>
       </c>
     </row>
-    <row r="16" spans="1:8">
-      <c r="A16" s="3" t="s">
+    <row r="16" ht="15.4" spans="1:8">
+      <c r="A16" s="12" t="s">
         <v>135</v>
       </c>
-      <c r="B16" s="3" t="s">
+      <c r="B16" s="12" t="s">
         <v>245</v>
       </c>
-      <c r="C16" s="3" t="s">
+      <c r="C16" s="12" t="s">
         <v>246</v>
       </c>
-      <c r="D16" s="5">
+      <c r="D16" s="21">
         <v>26</v>
       </c>
-      <c r="E16" s="5">
-        <v>31</v>
-      </c>
-      <c r="F16" s="5">
-        <v>31</v>
-      </c>
-      <c r="G16" s="9">
+      <c r="E16" s="21">
+        <v>31</v>
+      </c>
+      <c r="F16" s="21">
+        <v>31</v>
+      </c>
+      <c r="G16" s="22">
         <v>83.8709677419355</v>
       </c>
-      <c r="H16" s="9">
+      <c r="H16" s="22">
         <v>83.8709677419355</v>
       </c>
     </row>
-    <row r="17" spans="1:8">
-      <c r="A17" s="3" t="s">
+    <row r="17" ht="15.4" spans="1:8">
+      <c r="A17" s="12" t="s">
         <v>135</v>
       </c>
-      <c r="B17" s="3" t="s">
+      <c r="B17" s="12" t="s">
         <v>245</v>
       </c>
-      <c r="C17" s="3" t="s">
+      <c r="C17" s="12" t="s">
         <v>247</v>
       </c>
-      <c r="D17" s="5">
+      <c r="D17" s="21">
         <v>1</v>
       </c>
-      <c r="E17" s="5">
-        <v>31</v>
-      </c>
-      <c r="F17" s="5">
-        <v>31</v>
-      </c>
-      <c r="G17" s="9">
+      <c r="E17" s="21">
+        <v>31</v>
+      </c>
+      <c r="F17" s="21">
+        <v>31</v>
+      </c>
+      <c r="G17" s="22">
         <v>3.2258064516129</v>
       </c>
-      <c r="H17" s="9">
+      <c r="H17" s="22">
         <v>3.2258064516129</v>
       </c>
     </row>
-    <row r="18" spans="1:8">
-      <c r="A18" s="3" t="s">
+    <row r="18" ht="15.4" spans="1:8">
+      <c r="A18" s="12" t="s">
         <v>135</v>
       </c>
-      <c r="B18" s="3" t="s">
+      <c r="B18" s="12" t="s">
         <v>245</v>
       </c>
-      <c r="C18" s="3" t="s">
+      <c r="C18" s="12" t="s">
         <v>248</v>
       </c>
-      <c r="D18" s="5">
+      <c r="D18" s="21">
         <v>4</v>
       </c>
-      <c r="E18" s="5">
-        <v>31</v>
-      </c>
-      <c r="F18" s="5">
-        <v>31</v>
-      </c>
-      <c r="G18" s="9">
+      <c r="E18" s="21">
+        <v>31</v>
+      </c>
+      <c r="F18" s="21">
+        <v>31</v>
+      </c>
+      <c r="G18" s="22">
         <v>12.9032258064516</v>
       </c>
-      <c r="H18" s="9">
+      <c r="H18" s="22">
         <v>12.9032258064516</v>
       </c>
     </row>
-    <row r="19" spans="1:8">
-      <c r="A19" s="3" t="s">
+    <row r="19" ht="15.4" spans="1:8">
+      <c r="A19" s="12" t="s">
         <v>136</v>
       </c>
-      <c r="B19" s="3" t="s">
+      <c r="B19" s="12" t="s">
         <v>249</v>
       </c>
-      <c r="C19" s="3" t="s">
+      <c r="C19" s="12" t="s">
         <v>250</v>
       </c>
-      <c r="D19" s="5">
+      <c r="D19" s="21">
         <v>10</v>
       </c>
-      <c r="E19" s="5">
-        <v>31</v>
-      </c>
-      <c r="F19" s="5">
-        <v>31</v>
-      </c>
-      <c r="G19" s="9">
+      <c r="E19" s="21">
+        <v>31</v>
+      </c>
+      <c r="F19" s="21">
+        <v>31</v>
+      </c>
+      <c r="G19" s="22">
         <v>32.258064516129</v>
       </c>
-      <c r="H19" s="9">
+      <c r="H19" s="22">
         <v>32.258064516129</v>
       </c>
     </row>
-    <row r="20" spans="1:8">
-      <c r="A20" s="3" t="s">
+    <row r="20" ht="15.4" spans="1:8">
+      <c r="A20" s="12" t="s">
         <v>136</v>
       </c>
-      <c r="B20" s="3" t="s">
+      <c r="B20" s="12" t="s">
         <v>249</v>
       </c>
-      <c r="C20" s="3" t="s">
+      <c r="C20" s="12" t="s">
         <v>251</v>
       </c>
-      <c r="D20" s="5">
+      <c r="D20" s="21">
         <v>3</v>
       </c>
-      <c r="E20" s="5">
-        <v>31</v>
-      </c>
-      <c r="F20" s="5">
-        <v>31</v>
-      </c>
-      <c r="G20" s="9">
+      <c r="E20" s="21">
+        <v>31</v>
+      </c>
+      <c r="F20" s="21">
+        <v>31</v>
+      </c>
+      <c r="G20" s="22">
         <v>9.67741935483871</v>
       </c>
-      <c r="H20" s="9">
+      <c r="H20" s="22">
         <v>9.67741935483871</v>
       </c>
     </row>
-    <row r="21" spans="1:8">
-      <c r="A21" s="3" t="s">
+    <row r="21" ht="15.4" spans="1:8">
+      <c r="A21" s="12" t="s">
         <v>136</v>
       </c>
-      <c r="B21" s="3" t="s">
+      <c r="B21" s="12" t="s">
         <v>249</v>
       </c>
-      <c r="C21" s="3" t="s">
+      <c r="C21" s="12" t="s">
         <v>252</v>
       </c>
-      <c r="D21" s="5">
+      <c r="D21" s="21">
         <v>5</v>
       </c>
-      <c r="E21" s="5">
-        <v>31</v>
-      </c>
-      <c r="F21" s="5">
-        <v>31</v>
-      </c>
-      <c r="G21" s="9">
+      <c r="E21" s="21">
+        <v>31</v>
+      </c>
+      <c r="F21" s="21">
+        <v>31</v>
+      </c>
+      <c r="G21" s="22">
         <v>16.1290322580645</v>
       </c>
-      <c r="H21" s="9">
+      <c r="H21" s="22">
         <v>16.1290322580645</v>
       </c>
     </row>
-    <row r="22" spans="1:8">
-      <c r="A22" s="3" t="s">
+    <row r="22" ht="15.4" spans="1:8">
+      <c r="A22" s="12" t="s">
         <v>136</v>
       </c>
-      <c r="B22" s="3" t="s">
+      <c r="B22" s="12" t="s">
         <v>249</v>
       </c>
-      <c r="C22" s="3" t="s">
+      <c r="C22" s="12" t="s">
         <v>253</v>
       </c>
-      <c r="D22" s="5">
+      <c r="D22" s="21">
         <v>11</v>
       </c>
-      <c r="E22" s="5">
-        <v>31</v>
-      </c>
-      <c r="F22" s="5">
-        <v>31</v>
-      </c>
-      <c r="G22" s="9">
+      <c r="E22" s="21">
+        <v>31</v>
+      </c>
+      <c r="F22" s="21">
+        <v>31</v>
+      </c>
+      <c r="G22" s="22">
         <v>35.4838709677419</v>
       </c>
-      <c r="H22" s="9">
+      <c r="H22" s="22">
         <v>35.4838709677419</v>
       </c>
     </row>
-    <row r="23" spans="1:8">
-      <c r="A23" s="3" t="s">
+    <row r="23" ht="15.4" spans="1:8">
+      <c r="A23" s="12" t="s">
         <v>136</v>
       </c>
-      <c r="B23" s="3" t="s">
+      <c r="B23" s="12" t="s">
         <v>249</v>
       </c>
-      <c r="C23" s="3" t="s">
+      <c r="C23" s="12" t="s">
         <v>254</v>
       </c>
-      <c r="D23" s="5">
+      <c r="D23" s="21">
         <v>2</v>
       </c>
-      <c r="E23" s="5">
-        <v>31</v>
-      </c>
-      <c r="F23" s="5">
-        <v>31</v>
-      </c>
-      <c r="G23" s="9">
+      <c r="E23" s="21">
+        <v>31</v>
+      </c>
+      <c r="F23" s="21">
+        <v>31</v>
+      </c>
+      <c r="G23" s="22">
         <v>6.45161290322581</v>
       </c>
-      <c r="H23" s="9">
+      <c r="H23" s="22">
         <v>6.45161290322581</v>
       </c>
     </row>
-    <row r="24" spans="1:8">
-      <c r="A24" s="3" t="s">
+    <row r="24" ht="15.4" spans="1:8">
+      <c r="A24" s="12" t="s">
         <v>137</v>
       </c>
-      <c r="B24" s="3" t="s">
+      <c r="B24" s="12" t="s">
         <v>255</v>
       </c>
-      <c r="C24" s="3" t="s">
+      <c r="C24" s="12" t="s">
         <v>256</v>
       </c>
-      <c r="D24" s="5">
+      <c r="D24" s="21">
         <v>2</v>
       </c>
-      <c r="E24" s="5">
-        <v>31</v>
-      </c>
-      <c r="F24" s="5">
-        <v>31</v>
-      </c>
-      <c r="G24" s="9">
+      <c r="E24" s="21">
+        <v>31</v>
+      </c>
+      <c r="F24" s="21">
+        <v>31</v>
+      </c>
+      <c r="G24" s="22">
         <v>6.45161290322581</v>
       </c>
-      <c r="H24" s="9">
+      <c r="H24" s="22">
         <v>6.45161290322581</v>
       </c>
     </row>
-    <row r="25" spans="1:8">
-      <c r="A25" s="3" t="s">
+    <row r="25" ht="15.4" spans="1:8">
+      <c r="A25" s="12" t="s">
         <v>137</v>
       </c>
-      <c r="B25" s="3" t="s">
+      <c r="B25" s="12" t="s">
         <v>255</v>
       </c>
-      <c r="C25" s="3" t="s">
+      <c r="C25" s="12" t="s">
         <v>257</v>
       </c>
-      <c r="D25" s="5">
+      <c r="D25" s="21">
         <v>6</v>
       </c>
-      <c r="E25" s="5">
-        <v>31</v>
-      </c>
-      <c r="F25" s="5">
-        <v>31</v>
-      </c>
-      <c r="G25" s="9">
+      <c r="E25" s="21">
+        <v>31</v>
+      </c>
+      <c r="F25" s="21">
+        <v>31</v>
+      </c>
+      <c r="G25" s="22">
         <v>19.3548387096774</v>
       </c>
-      <c r="H25" s="9">
+      <c r="H25" s="22">
         <v>19.3548387096774</v>
       </c>
     </row>
-    <row r="26" spans="1:8">
-      <c r="A26" s="3" t="s">
+    <row r="26" ht="15.4" spans="1:8">
+      <c r="A26" s="12" t="s">
         <v>137</v>
       </c>
-      <c r="B26" s="3" t="s">
+      <c r="B26" s="12" t="s">
         <v>255</v>
       </c>
-      <c r="C26" s="3" t="s">
+      <c r="C26" s="12" t="s">
         <v>258</v>
       </c>
-      <c r="D26" s="5">
+      <c r="D26" s="21">
         <v>6</v>
       </c>
-      <c r="E26" s="5">
-        <v>31</v>
-      </c>
-      <c r="F26" s="5">
-        <v>31</v>
-      </c>
-      <c r="G26" s="9">
+      <c r="E26" s="21">
+        <v>31</v>
+      </c>
+      <c r="F26" s="21">
+        <v>31</v>
+      </c>
+      <c r="G26" s="22">
         <v>19.3548387096774</v>
       </c>
-      <c r="H26" s="9">
+      <c r="H26" s="22">
         <v>19.3548387096774</v>
       </c>
     </row>
-    <row r="27" spans="1:8">
-      <c r="A27" s="3" t="s">
+    <row r="27" ht="15.4" spans="1:8">
+      <c r="A27" s="12" t="s">
         <v>137</v>
       </c>
-      <c r="B27" s="3" t="s">
+      <c r="B27" s="12" t="s">
         <v>255</v>
       </c>
-      <c r="C27" s="3" t="s">
+      <c r="C27" s="12" t="s">
         <v>259</v>
       </c>
-      <c r="D27" s="5">
+      <c r="D27" s="21">
         <v>17</v>
       </c>
-      <c r="E27" s="5">
-        <v>31</v>
-      </c>
-      <c r="F27" s="5">
-        <v>31</v>
-      </c>
-      <c r="G27" s="9">
+      <c r="E27" s="21">
+        <v>31</v>
+      </c>
+      <c r="F27" s="21">
+        <v>31</v>
+      </c>
+      <c r="G27" s="22">
         <v>54.8387096774194</v>
       </c>
-      <c r="H27" s="9">
+      <c r="H27" s="22">
         <v>54.8387096774194</v>
       </c>
     </row>
-    <row r="28" spans="1:8">
-      <c r="A28" s="3" t="s">
+    <row r="28" ht="15.4" spans="1:8">
+      <c r="A28" s="12" t="s">
         <v>138</v>
       </c>
-      <c r="B28" s="3" t="s">
+      <c r="B28" s="12" t="s">
         <v>260</v>
       </c>
-      <c r="C28" s="3" t="s">
+      <c r="C28" s="12" t="s">
         <v>261</v>
       </c>
-      <c r="D28" s="5">
+      <c r="D28" s="21">
         <v>9</v>
       </c>
-      <c r="E28" s="5">
-        <v>31</v>
-      </c>
-      <c r="F28" s="5">
-        <v>31</v>
-      </c>
-      <c r="G28" s="9">
+      <c r="E28" s="21">
+        <v>31</v>
+      </c>
+      <c r="F28" s="21">
+        <v>31</v>
+      </c>
+      <c r="G28" s="22">
         <v>29.0322580645161</v>
       </c>
-      <c r="H28" s="9">
+      <c r="H28" s="22">
         <v>29.0322580645161</v>
       </c>
     </row>
-    <row r="29" spans="1:8">
-      <c r="A29" s="3" t="s">
+    <row r="29" ht="15.4" spans="1:8">
+      <c r="A29" s="12" t="s">
         <v>138</v>
       </c>
-      <c r="B29" s="3" t="s">
+      <c r="B29" s="12" t="s">
         <v>260</v>
       </c>
-      <c r="C29" s="3" t="s">
+      <c r="C29" s="12" t="s">
         <v>262</v>
       </c>
-      <c r="D29" s="5">
+      <c r="D29" s="21">
         <v>14</v>
       </c>
-      <c r="E29" s="5">
-        <v>31</v>
-      </c>
-      <c r="F29" s="5">
-        <v>31</v>
-      </c>
-      <c r="G29" s="9">
+      <c r="E29" s="21">
+        <v>31</v>
+      </c>
+      <c r="F29" s="21">
+        <v>31</v>
+      </c>
+      <c r="G29" s="22">
         <v>45.1612903225806</v>
       </c>
-      <c r="H29" s="9">
+      <c r="H29" s="22">
         <v>45.1612903225806</v>
       </c>
     </row>
-    <row r="30" spans="1:8">
-      <c r="A30" s="3" t="s">
+    <row r="30" ht="15.4" spans="1:8">
+      <c r="A30" s="12" t="s">
         <v>138</v>
       </c>
-      <c r="B30" s="3" t="s">
+      <c r="B30" s="12" t="s">
         <v>260</v>
       </c>
-      <c r="C30" s="3" t="s">
+      <c r="C30" s="12" t="s">
         <v>263</v>
       </c>
-      <c r="D30" s="5">
+      <c r="D30" s="21">
         <v>6</v>
       </c>
-      <c r="E30" s="5">
-        <v>31</v>
-      </c>
-      <c r="F30" s="5">
-        <v>31</v>
-      </c>
-      <c r="G30" s="9">
+      <c r="E30" s="21">
+        <v>31</v>
+      </c>
+      <c r="F30" s="21">
+        <v>31</v>
+      </c>
+      <c r="G30" s="22">
         <v>19.3548387096774</v>
       </c>
-      <c r="H30" s="9">
+      <c r="H30" s="22">
         <v>19.3548387096774</v>
       </c>
     </row>
-    <row r="31" spans="1:8">
-      <c r="A31" s="3" t="s">
+    <row r="31" ht="15.4" spans="1:8">
+      <c r="A31" s="12" t="s">
         <v>138</v>
       </c>
-      <c r="B31" s="3" t="s">
+      <c r="B31" s="12" t="s">
         <v>260</v>
       </c>
-      <c r="C31" s="3" t="s">
+      <c r="C31" s="12" t="s">
         <v>264</v>
       </c>
-      <c r="D31" s="5">
+      <c r="D31" s="21">
         <v>2</v>
       </c>
-      <c r="E31" s="5">
-        <v>31</v>
-      </c>
-      <c r="F31" s="5">
-        <v>31</v>
-      </c>
-      <c r="G31" s="9">
+      <c r="E31" s="21">
+        <v>31</v>
+      </c>
+      <c r="F31" s="21">
+        <v>31</v>
+      </c>
+      <c r="G31" s="22">
         <v>6.45161290322581</v>
       </c>
-      <c r="H31" s="9">
+      <c r="H31" s="22">
         <v>6.45161290322581</v>
       </c>
     </row>
-    <row r="32" spans="1:8">
-      <c r="A32" s="3" t="s">
+    <row r="32" ht="15.4" spans="1:8">
+      <c r="A32" s="12" t="s">
         <v>140</v>
       </c>
-      <c r="B32" s="3" t="s">
+      <c r="B32" s="12" t="s">
         <v>265</v>
       </c>
-      <c r="C32" s="3" t="s">
+      <c r="C32" s="12" t="s">
         <v>266</v>
       </c>
-      <c r="D32" s="5">
+      <c r="D32" s="21">
         <v>24</v>
       </c>
-      <c r="E32" s="5">
-        <v>31</v>
-      </c>
-      <c r="F32" s="5">
-        <v>31</v>
-      </c>
-      <c r="G32" s="9">
+      <c r="E32" s="21">
+        <v>31</v>
+      </c>
+      <c r="F32" s="21">
+        <v>31</v>
+      </c>
+      <c r="G32" s="22">
         <v>77.4193548387097</v>
       </c>
-      <c r="H32" s="9">
+      <c r="H32" s="22">
         <v>77.4193548387097</v>
       </c>
     </row>
-    <row r="33" spans="1:8">
-      <c r="A33" s="3" t="s">
+    <row r="33" ht="15.4" spans="1:8">
+      <c r="A33" s="12" t="s">
         <v>140</v>
       </c>
-      <c r="B33" s="3" t="s">
+      <c r="B33" s="12" t="s">
         <v>265</v>
       </c>
-      <c r="C33" s="3" t="s">
+      <c r="C33" s="12" t="s">
         <v>267</v>
       </c>
-      <c r="D33" s="5">
+      <c r="D33" s="21">
         <v>2</v>
       </c>
-      <c r="E33" s="5">
-        <v>31</v>
-      </c>
-      <c r="F33" s="5">
-        <v>31</v>
-      </c>
-      <c r="G33" s="9">
+      <c r="E33" s="21">
+        <v>31</v>
+      </c>
+      <c r="F33" s="21">
+        <v>31</v>
+      </c>
+      <c r="G33" s="22">
         <v>6.45161290322581</v>
       </c>
-      <c r="H33" s="9">
+      <c r="H33" s="22">
         <v>6.45161290322581</v>
       </c>
     </row>
-    <row r="34" spans="1:8">
-      <c r="A34" s="3" t="s">
+    <row r="34" ht="15.4" spans="1:8">
+      <c r="A34" s="12" t="s">
         <v>140</v>
       </c>
-      <c r="B34" s="3" t="s">
+      <c r="B34" s="12" t="s">
         <v>265</v>
       </c>
-      <c r="C34" s="3" t="s">
+      <c r="C34" s="12" t="s">
         <v>268</v>
       </c>
-      <c r="D34" s="5">
+      <c r="D34" s="21">
         <v>4</v>
       </c>
-      <c r="E34" s="5">
-        <v>31</v>
-      </c>
-      <c r="F34" s="5">
-        <v>31</v>
-      </c>
-      <c r="G34" s="9">
+      <c r="E34" s="21">
+        <v>31</v>
+      </c>
+      <c r="F34" s="21">
+        <v>31</v>
+      </c>
+      <c r="G34" s="22">
         <v>12.9032258064516</v>
       </c>
-      <c r="H34" s="9">
+      <c r="H34" s="22">
         <v>12.9032258064516</v>
       </c>
     </row>
-    <row r="35" spans="1:8">
-      <c r="A35" s="3" t="s">
+    <row r="35" ht="15.4" spans="1:8">
+      <c r="A35" s="12" t="s">
         <v>140</v>
       </c>
-      <c r="B35" s="3" t="s">
+      <c r="B35" s="12" t="s">
         <v>265</v>
       </c>
-      <c r="C35" s="3" t="s">
+      <c r="C35" s="12" t="s">
         <v>269</v>
       </c>
-      <c r="D35" s="5">
+      <c r="D35" s="21">
         <v>1</v>
       </c>
-      <c r="E35" s="5">
-        <v>31</v>
-      </c>
-      <c r="F35" s="5">
-        <v>31</v>
-      </c>
-      <c r="G35" s="9">
+      <c r="E35" s="21">
+        <v>31</v>
+      </c>
+      <c r="F35" s="21">
+        <v>31</v>
+      </c>
+      <c r="G35" s="22">
         <v>3.2258064516129</v>
       </c>
-      <c r="H35" s="9">
+      <c r="H35" s="22">
         <v>3.2258064516129</v>
       </c>
     </row>
-    <row r="36" spans="1:8">
-      <c r="A36" s="3" t="s">
+    <row r="36" ht="30.75" spans="1:8">
+      <c r="A36" s="12" t="s">
         <v>141</v>
       </c>
-      <c r="B36" s="3" t="s">
+      <c r="B36" s="12" t="s">
         <v>270</v>
       </c>
-      <c r="C36" s="3" t="s">
+      <c r="C36" s="12" t="s">
         <v>266</v>
       </c>
-      <c r="D36" s="5">
+      <c r="D36" s="21">
         <v>20</v>
       </c>
-      <c r="E36" s="5">
-        <v>31</v>
-      </c>
-      <c r="F36" s="5">
-        <v>31</v>
-      </c>
-      <c r="G36" s="9">
+      <c r="E36" s="21">
+        <v>31</v>
+      </c>
+      <c r="F36" s="21">
+        <v>31</v>
+      </c>
+      <c r="G36" s="22">
         <v>64.5161290322581</v>
       </c>
-      <c r="H36" s="9">
+      <c r="H36" s="22">
         <v>64.5161290322581</v>
       </c>
     </row>
-    <row r="37" spans="1:8">
-      <c r="A37" s="3" t="s">
+    <row r="37" ht="30.75" spans="1:8">
+      <c r="A37" s="12" t="s">
         <v>141</v>
       </c>
-      <c r="B37" s="3" t="s">
+      <c r="B37" s="12" t="s">
         <v>270</v>
       </c>
-      <c r="C37" s="3" t="s">
+      <c r="C37" s="12" t="s">
         <v>267</v>
       </c>
-      <c r="D37" s="5">
+      <c r="D37" s="21">
         <v>3</v>
       </c>
-      <c r="E37" s="5">
-        <v>31</v>
-      </c>
-      <c r="F37" s="5">
-        <v>31</v>
-      </c>
-      <c r="G37" s="9">
+      <c r="E37" s="21">
+        <v>31</v>
+      </c>
+      <c r="F37" s="21">
+        <v>31</v>
+      </c>
+      <c r="G37" s="22">
         <v>9.67741935483871</v>
       </c>
-      <c r="H37" s="9">
+      <c r="H37" s="22">
         <v>9.67741935483871</v>
       </c>
     </row>
-    <row r="38" spans="1:8">
-      <c r="A38" s="3" t="s">
+    <row r="38" ht="30.75" spans="1:8">
+      <c r="A38" s="12" t="s">
         <v>141</v>
       </c>
-      <c r="B38" s="3" t="s">
+      <c r="B38" s="12" t="s">
         <v>270</v>
       </c>
-      <c r="C38" s="3" t="s">
+      <c r="C38" s="12" t="s">
         <v>268</v>
       </c>
-      <c r="D38" s="5">
+      <c r="D38" s="21">
         <v>7</v>
       </c>
-      <c r="E38" s="5">
-        <v>31</v>
-      </c>
-      <c r="F38" s="5">
-        <v>31</v>
-      </c>
-      <c r="G38" s="9">
+      <c r="E38" s="21">
+        <v>31</v>
+      </c>
+      <c r="F38" s="21">
+        <v>31</v>
+      </c>
+      <c r="G38" s="22">
         <v>22.5806451612903</v>
       </c>
-      <c r="H38" s="9">
+      <c r="H38" s="22">
         <v>22.5806451612903</v>
       </c>
     </row>
-    <row r="39" spans="1:8">
-      <c r="A39" s="3" t="s">
+    <row r="39" ht="30.75" spans="1:8">
+      <c r="A39" s="12" t="s">
         <v>141</v>
       </c>
-      <c r="B39" s="3" t="s">
+      <c r="B39" s="12" t="s">
         <v>270</v>
       </c>
-      <c r="C39" s="3" t="s">
+      <c r="C39" s="12" t="s">
         <v>269</v>
       </c>
-      <c r="D39" s="5">
+      <c r="D39" s="21">
         <v>1</v>
       </c>
-      <c r="E39" s="5">
-        <v>31</v>
-      </c>
-      <c r="F39" s="5">
-        <v>31</v>
-      </c>
-      <c r="G39" s="9">
+      <c r="E39" s="21">
+        <v>31</v>
+      </c>
+      <c r="F39" s="21">
+        <v>31</v>
+      </c>
+      <c r="G39" s="22">
         <v>3.2258064516129</v>
       </c>
-      <c r="H39" s="9">
+      <c r="H39" s="22">
         <v>3.2258064516129</v>
       </c>
     </row>
-    <row r="40" spans="1:8">
-      <c r="A40" s="3" t="s">
+    <row r="40" ht="15.4" spans="1:8">
+      <c r="A40" s="12" t="s">
         <v>142</v>
       </c>
-      <c r="B40" s="3" t="s">
+      <c r="B40" s="12" t="s">
         <v>271</v>
       </c>
-      <c r="C40" s="3" t="s">
+      <c r="C40" s="12" t="s">
         <v>272</v>
       </c>
-      <c r="D40" s="5">
+      <c r="D40" s="21">
         <v>3</v>
       </c>
-      <c r="E40" s="5">
-        <v>31</v>
-      </c>
-      <c r="F40" s="5">
-        <v>31</v>
-      </c>
-      <c r="G40" s="9">
+      <c r="E40" s="21">
+        <v>31</v>
+      </c>
+      <c r="F40" s="21">
+        <v>31</v>
+      </c>
+      <c r="G40" s="22">
         <v>9.67741935483871</v>
       </c>
-      <c r="H40" s="9">
+      <c r="H40" s="22">
         <v>9.67741935483871</v>
       </c>
     </row>
-    <row r="41" spans="1:8">
-      <c r="A41" s="3" t="s">
+    <row r="41" ht="15.4" spans="1:8">
+      <c r="A41" s="12" t="s">
         <v>142</v>
       </c>
-      <c r="B41" s="3" t="s">
+      <c r="B41" s="12" t="s">
         <v>271</v>
       </c>
-      <c r="C41" s="3" t="s">
+      <c r="C41" s="12" t="s">
         <v>273</v>
       </c>
-      <c r="D41" s="5">
+      <c r="D41" s="21">
         <v>6</v>
       </c>
-      <c r="E41" s="5">
-        <v>31</v>
-      </c>
-      <c r="F41" s="5">
-        <v>31</v>
-      </c>
-      <c r="G41" s="9">
+      <c r="E41" s="21">
+        <v>31</v>
+      </c>
+      <c r="F41" s="21">
+        <v>31</v>
+      </c>
+      <c r="G41" s="22">
         <v>19.3548387096774</v>
       </c>
-      <c r="H41" s="9">
+      <c r="H41" s="22">
         <v>19.3548387096774</v>
       </c>
     </row>
-    <row r="42" spans="1:8">
-      <c r="A42" s="3" t="s">
+    <row r="42" ht="15.4" spans="1:8">
+      <c r="A42" s="12" t="s">
         <v>142</v>
       </c>
-      <c r="B42" s="3" t="s">
+      <c r="B42" s="12" t="s">
         <v>271</v>
       </c>
-      <c r="C42" s="3" t="s">
+      <c r="C42" s="12" t="s">
         <v>274</v>
       </c>
-      <c r="D42" s="5">
+      <c r="D42" s="21">
         <v>19</v>
       </c>
-      <c r="E42" s="5">
-        <v>31</v>
-      </c>
-      <c r="F42" s="5">
-        <v>31</v>
-      </c>
-      <c r="G42" s="9">
+      <c r="E42" s="21">
+        <v>31</v>
+      </c>
+      <c r="F42" s="21">
+        <v>31</v>
+      </c>
+      <c r="G42" s="22">
         <v>61.2903225806452</v>
       </c>
-      <c r="H42" s="9">
+      <c r="H42" s="22">
         <v>61.2903225806452</v>
       </c>
     </row>
-    <row r="43" spans="1:8">
-      <c r="A43" s="3" t="s">
+    <row r="43" ht="15.4" spans="1:8">
+      <c r="A43" s="12" t="s">
         <v>142</v>
       </c>
-      <c r="B43" s="3" t="s">
+      <c r="B43" s="12" t="s">
         <v>271</v>
       </c>
-      <c r="C43" s="3" t="s">
+      <c r="C43" s="12" t="s">
         <v>275</v>
       </c>
-      <c r="D43" s="5">
+      <c r="D43" s="21">
         <v>3</v>
       </c>
-      <c r="E43" s="5">
-        <v>31</v>
-      </c>
-      <c r="F43" s="5">
-        <v>31</v>
-      </c>
-      <c r="G43" s="9">
+      <c r="E43" s="21">
+        <v>31</v>
+      </c>
+      <c r="F43" s="21">
+        <v>31</v>
+      </c>
+      <c r="G43" s="22">
         <v>9.67741935483871</v>
       </c>
-      <c r="H43" s="9">
+      <c r="H43" s="22">
         <v>9.67741935483871</v>
       </c>
     </row>
-    <row r="44" spans="1:8">
-      <c r="A44" s="3" t="s">
+    <row r="44" ht="30.75" spans="1:8">
+      <c r="A44" s="12" t="s">
         <v>143</v>
       </c>
-      <c r="B44" s="3" t="s">
+      <c r="B44" s="12" t="s">
         <v>276</v>
       </c>
-      <c r="C44" s="3" t="s">
+      <c r="C44" s="12" t="s">
         <v>261</v>
       </c>
-      <c r="D44" s="5">
+      <c r="D44" s="21">
         <v>2</v>
       </c>
-      <c r="E44" s="5">
-        <v>31</v>
-      </c>
-      <c r="F44" s="5">
-        <v>31</v>
-      </c>
-      <c r="G44" s="9">
+      <c r="E44" s="21">
+        <v>31</v>
+      </c>
+      <c r="F44" s="21">
+        <v>31</v>
+      </c>
+      <c r="G44" s="22">
         <v>6.45161290322581</v>
       </c>
-      <c r="H44" s="9">
+      <c r="H44" s="22">
         <v>6.45161290322581</v>
       </c>
     </row>
-    <row r="45" spans="1:8">
-      <c r="A45" s="3" t="s">
+    <row r="45" ht="30.75" spans="1:8">
+      <c r="A45" s="12" t="s">
         <v>143</v>
       </c>
-      <c r="B45" s="3" t="s">
+      <c r="B45" s="12" t="s">
         <v>276</v>
       </c>
-      <c r="C45" s="3" t="s">
+      <c r="C45" s="12" t="s">
         <v>262</v>
       </c>
-      <c r="D45" s="5">
+      <c r="D45" s="21">
         <v>22</v>
       </c>
-      <c r="E45" s="5">
-        <v>31</v>
-      </c>
-      <c r="F45" s="5">
-        <v>31</v>
-      </c>
-      <c r="G45" s="9">
+      <c r="E45" s="21">
+        <v>31</v>
+      </c>
+      <c r="F45" s="21">
+        <v>31</v>
+      </c>
+      <c r="G45" s="22">
         <v>70.9677419354839</v>
       </c>
-      <c r="H45" s="9">
+      <c r="H45" s="22">
         <v>70.9677419354839</v>
       </c>
     </row>
-    <row r="46" spans="1:8">
-      <c r="A46" s="3" t="s">
+    <row r="46" ht="30.75" spans="1:8">
+      <c r="A46" s="12" t="s">
         <v>143</v>
       </c>
-      <c r="B46" s="3" t="s">
+      <c r="B46" s="12" t="s">
         <v>276</v>
       </c>
-      <c r="C46" s="3" t="s">
+      <c r="C46" s="12" t="s">
         <v>263</v>
       </c>
-      <c r="D46" s="5">
+      <c r="D46" s="21">
         <v>2</v>
       </c>
-      <c r="E46" s="5">
-        <v>31</v>
-      </c>
-      <c r="F46" s="5">
-        <v>31</v>
-      </c>
-      <c r="G46" s="9">
+      <c r="E46" s="21">
+        <v>31</v>
+      </c>
+      <c r="F46" s="21">
+        <v>31</v>
+      </c>
+      <c r="G46" s="22">
         <v>6.45161290322581</v>
       </c>
-      <c r="H46" s="9">
+      <c r="H46" s="22">
         <v>6.45161290322581</v>
       </c>
     </row>
-    <row r="47" spans="1:8">
-      <c r="A47" s="3" t="s">
+    <row r="47" ht="30.75" spans="1:8">
+      <c r="A47" s="12" t="s">
         <v>143</v>
       </c>
-      <c r="B47" s="3" t="s">
+      <c r="B47" s="12" t="s">
         <v>276</v>
       </c>
-      <c r="C47" s="3" t="s">
+      <c r="C47" s="12" t="s">
         <v>264</v>
       </c>
-      <c r="D47" s="5">
+      <c r="D47" s="21">
         <v>5</v>
       </c>
-      <c r="E47" s="5">
-        <v>31</v>
-      </c>
-      <c r="F47" s="5">
-        <v>31</v>
-      </c>
-      <c r="G47" s="9">
+      <c r="E47" s="21">
+        <v>31</v>
+      </c>
+      <c r="F47" s="21">
+        <v>31</v>
+      </c>
+      <c r="G47" s="22">
         <v>16.1290322580645</v>
       </c>
-      <c r="H47" s="9">
+      <c r="H47" s="22">
         <v>16.1290322580645</v>
       </c>
     </row>
-    <row r="48" spans="1:8">
-      <c r="A48" s="3" t="s">
+    <row r="48" ht="15.4" spans="1:8">
+      <c r="A48" s="12" t="s">
         <v>144</v>
       </c>
-      <c r="B48" s="3" t="s">
+      <c r="B48" s="12" t="s">
         <v>277</v>
       </c>
-      <c r="C48" s="3" t="s">
+      <c r="C48" s="12" t="s">
         <v>261</v>
       </c>
-      <c r="D48" s="5">
+      <c r="D48" s="21">
         <v>4</v>
       </c>
-      <c r="E48" s="5">
-        <v>31</v>
-      </c>
-      <c r="F48" s="5">
-        <v>31</v>
-      </c>
-      <c r="G48" s="9">
+      <c r="E48" s="21">
+        <v>31</v>
+      </c>
+      <c r="F48" s="21">
+        <v>31</v>
+      </c>
+      <c r="G48" s="22">
         <v>12.9032258064516</v>
       </c>
-      <c r="H48" s="9">
+      <c r="H48" s="22">
         <v>12.9032258064516</v>
       </c>
     </row>
-    <row r="49" spans="1:8">
-      <c r="A49" s="3" t="s">
+    <row r="49" ht="15.4" spans="1:8">
+      <c r="A49" s="12" t="s">
         <v>144</v>
       </c>
-      <c r="B49" s="3" t="s">
+      <c r="B49" s="12" t="s">
         <v>277</v>
       </c>
-      <c r="C49" s="3" t="s">
+      <c r="C49" s="12" t="s">
         <v>262</v>
       </c>
-      <c r="D49" s="5">
+      <c r="D49" s="21">
         <v>12</v>
       </c>
-      <c r="E49" s="5">
-        <v>31</v>
-      </c>
-      <c r="F49" s="5">
-        <v>31</v>
-      </c>
-      <c r="G49" s="9">
+      <c r="E49" s="21">
+        <v>31</v>
+      </c>
+      <c r="F49" s="21">
+        <v>31</v>
+      </c>
+      <c r="G49" s="22">
         <v>38.7096774193548</v>
       </c>
-      <c r="H49" s="9">
+      <c r="H49" s="22">
         <v>38.7096774193548</v>
       </c>
     </row>
-    <row r="50" spans="1:8">
-      <c r="A50" s="3" t="s">
+    <row r="50" ht="15.4" spans="1:8">
+      <c r="A50" s="12" t="s">
         <v>144</v>
       </c>
-      <c r="B50" s="3" t="s">
+      <c r="B50" s="12" t="s">
         <v>277</v>
       </c>
-      <c r="C50" s="3" t="s">
+      <c r="C50" s="12" t="s">
         <v>263</v>
       </c>
-      <c r="D50" s="5">
+      <c r="D50" s="21">
         <v>4</v>
       </c>
-      <c r="E50" s="5">
-        <v>31</v>
-      </c>
-      <c r="F50" s="5">
-        <v>31</v>
-      </c>
-      <c r="G50" s="9">
+      <c r="E50" s="21">
+        <v>31</v>
+      </c>
+      <c r="F50" s="21">
+        <v>31</v>
+      </c>
+      <c r="G50" s="22">
         <v>12.9032258064516</v>
       </c>
-      <c r="H50" s="9">
+      <c r="H50" s="22">
         <v>12.9032258064516</v>
       </c>
     </row>
-    <row r="51" spans="1:8">
-      <c r="A51" s="3" t="s">
+    <row r="51" ht="15.4" spans="1:8">
+      <c r="A51" s="12" t="s">
         <v>144</v>
       </c>
-      <c r="B51" s="3" t="s">
+      <c r="B51" s="12" t="s">
         <v>277</v>
       </c>
-      <c r="C51" s="3" t="s">
+      <c r="C51" s="12" t="s">
         <v>264</v>
       </c>
-      <c r="D51" s="5">
+      <c r="D51" s="21">
         <v>10</v>
       </c>
-      <c r="E51" s="5">
-        <v>31</v>
-      </c>
-      <c r="F51" s="5">
-        <v>31</v>
-      </c>
-      <c r="G51" s="9">
+      <c r="E51" s="21">
+        <v>31</v>
+      </c>
+      <c r="F51" s="21">
+        <v>31</v>
+      </c>
+      <c r="G51" s="22">
         <v>32.258064516129</v>
       </c>
-      <c r="H51" s="9">
+      <c r="H51" s="22">
         <v>32.258064516129</v>
       </c>
     </row>
-    <row r="52" spans="1:8">
-      <c r="A52" s="3" t="s">
+    <row r="52" ht="15.4" spans="1:8">
+      <c r="A52" s="12" t="s">
         <v>144</v>
       </c>
-      <c r="B52" s="3" t="s">
+      <c r="B52" s="12" t="s">
         <v>277</v>
       </c>
-      <c r="C52" s="3" t="s">
+      <c r="C52" s="12" t="s">
         <v>269</v>
       </c>
-      <c r="D52" s="5">
+      <c r="D52" s="21">
         <v>1</v>
       </c>
-      <c r="E52" s="5">
-        <v>31</v>
-      </c>
-      <c r="F52" s="5">
-        <v>31</v>
-      </c>
-      <c r="G52" s="9">
+      <c r="E52" s="21">
+        <v>31</v>
+      </c>
+      <c r="F52" s="21">
+        <v>31</v>
+      </c>
+      <c r="G52" s="22">
         <v>3.2258064516129</v>
       </c>
-      <c r="H52" s="9">
+      <c r="H52" s="22">
         <v>3.2258064516129</v>
       </c>
     </row>
-    <row r="53" ht="28.5" spans="1:8">
-      <c r="A53" s="3" t="s">
+    <row r="53" ht="30.75" spans="1:8">
+      <c r="A53" s="12" t="s">
         <v>145</v>
       </c>
-      <c r="B53" s="3" t="s">
+      <c r="B53" s="12" t="s">
         <v>278</v>
       </c>
-      <c r="C53" s="3" t="s">
+      <c r="C53" s="12" t="s">
         <v>279</v>
       </c>
-      <c r="D53" s="5">
+      <c r="D53" s="21">
         <v>14</v>
       </c>
-      <c r="E53" s="5">
-        <v>31</v>
-      </c>
-      <c r="F53" s="5">
-        <v>31</v>
-      </c>
-      <c r="G53" s="9">
+      <c r="E53" s="21">
+        <v>31</v>
+      </c>
+      <c r="F53" s="21">
+        <v>31</v>
+      </c>
+      <c r="G53" s="22">
         <v>45.1612903225806</v>
       </c>
-      <c r="H53" s="9">
+      <c r="H53" s="22">
         <v>45.1612903225806</v>
       </c>
     </row>
-    <row r="54" ht="28.5" spans="1:8">
-      <c r="A54" s="3" t="s">
+    <row r="54" ht="30.75" spans="1:8">
+      <c r="A54" s="12" t="s">
         <v>145</v>
       </c>
-      <c r="B54" s="3" t="s">
+      <c r="B54" s="12" t="s">
         <v>278</v>
       </c>
-      <c r="C54" s="3" t="s">
+      <c r="C54" s="12" t="s">
         <v>280</v>
       </c>
-      <c r="D54" s="5">
+      <c r="D54" s="21">
         <v>9</v>
       </c>
-      <c r="E54" s="5">
-        <v>31</v>
-      </c>
-      <c r="F54" s="5">
-        <v>31</v>
-      </c>
-      <c r="G54" s="9">
+      <c r="E54" s="21">
+        <v>31</v>
+      </c>
+      <c r="F54" s="21">
+        <v>31</v>
+      </c>
+      <c r="G54" s="22">
         <v>29.0322580645161</v>
       </c>
-      <c r="H54" s="9">
+      <c r="H54" s="22">
         <v>29.0322580645161</v>
       </c>
     </row>
-    <row r="55" ht="28.5" spans="1:8">
-      <c r="A55" s="3" t="s">
+    <row r="55" ht="30.75" spans="1:8">
+      <c r="A55" s="12" t="s">
         <v>145</v>
       </c>
-      <c r="B55" s="3" t="s">
+      <c r="B55" s="12" t="s">
         <v>278</v>
       </c>
-      <c r="C55" s="3" t="s">
+      <c r="C55" s="12" t="s">
         <v>281</v>
       </c>
-      <c r="D55" s="5">
+      <c r="D55" s="21">
         <v>8</v>
       </c>
-      <c r="E55" s="5">
-        <v>31</v>
-      </c>
-      <c r="F55" s="5">
-        <v>31</v>
-      </c>
-      <c r="G55" s="9">
+      <c r="E55" s="21">
+        <v>31</v>
+      </c>
+      <c r="F55" s="21">
+        <v>31</v>
+      </c>
+      <c r="G55" s="22">
         <v>25.8064516129032</v>
       </c>
-      <c r="H55" s="9">
+      <c r="H55" s="22">
         <v>25.8064516129032</v>
       </c>
     </row>
-    <row r="56" spans="1:8">
-      <c r="A56" s="3" t="s">
+    <row r="56" ht="15.4" spans="1:8">
+      <c r="A56" s="12" t="s">
         <v>282</v>
       </c>
-      <c r="B56" s="3" t="s">
+      <c r="B56" s="12" t="s">
         <v>283</v>
       </c>
-      <c r="C56" s="3" t="s">
+      <c r="C56" s="12" t="s">
         <v>284</v>
       </c>
-      <c r="D56" s="5">
+      <c r="D56" s="21">
         <v>7</v>
       </c>
-      <c r="E56" s="5">
-        <v>31</v>
-      </c>
-      <c r="F56" s="5">
-        <v>31</v>
-      </c>
-      <c r="G56" s="9">
+      <c r="E56" s="21">
+        <v>31</v>
+      </c>
+      <c r="F56" s="21">
+        <v>31</v>
+      </c>
+      <c r="G56" s="22">
         <v>22.5806451612903</v>
       </c>
-      <c r="H56" s="9">
+      <c r="H56" s="22">
         <v>22.5806451612903</v>
       </c>
     </row>
-    <row r="57" spans="1:8">
-      <c r="A57" s="3" t="s">
+    <row r="57" ht="15.4" spans="1:8">
+      <c r="A57" s="12" t="s">
         <v>282</v>
       </c>
-      <c r="B57" s="3" t="s">
+      <c r="B57" s="12" t="s">
         <v>283</v>
       </c>
-      <c r="C57" s="3" t="s">
+      <c r="C57" s="12" t="s">
         <v>285</v>
       </c>
-      <c r="D57" s="5">
+      <c r="D57" s="21">
         <v>7</v>
       </c>
-      <c r="E57" s="5">
-        <v>31</v>
-      </c>
-      <c r="F57" s="5">
-        <v>31</v>
-      </c>
-      <c r="G57" s="9">
+      <c r="E57" s="21">
+        <v>31</v>
+      </c>
+      <c r="F57" s="21">
+        <v>31</v>
+      </c>
+      <c r="G57" s="22">
         <v>22.5806451612903</v>
       </c>
-      <c r="H57" s="9">
+      <c r="H57" s="22">
         <v>22.5806451612903</v>
       </c>
     </row>
-    <row r="58" spans="1:8">
-      <c r="A58" s="3" t="s">
+    <row r="58" ht="15.4" spans="1:8">
+      <c r="A58" s="12" t="s">
         <v>282</v>
       </c>
-      <c r="B58" s="3" t="s">
+      <c r="B58" s="12" t="s">
         <v>283</v>
       </c>
-      <c r="C58" s="3" t="s">
+      <c r="C58" s="12" t="s">
         <v>286</v>
       </c>
-      <c r="D58" s="5">
+      <c r="D58" s="21">
         <v>4</v>
       </c>
-      <c r="E58" s="5">
-        <v>31</v>
-      </c>
-      <c r="F58" s="5">
-        <v>31</v>
-      </c>
-      <c r="G58" s="9">
+      <c r="E58" s="21">
+        <v>31</v>
+      </c>
+      <c r="F58" s="21">
+        <v>31</v>
+      </c>
+      <c r="G58" s="22">
         <v>12.9032258064516</v>
       </c>
-      <c r="H58" s="9">
+      <c r="H58" s="22">
         <v>12.9032258064516</v>
       </c>
     </row>
-    <row r="59" spans="1:8">
-      <c r="A59" s="3" t="s">
+    <row r="59" ht="15.4" spans="1:8">
+      <c r="A59" s="12" t="s">
         <v>282</v>
       </c>
-      <c r="B59" s="3" t="s">
+      <c r="B59" s="12" t="s">
         <v>283</v>
       </c>
-      <c r="C59" s="3" t="s">
+      <c r="C59" s="12" t="s">
         <v>287</v>
       </c>
-      <c r="D59" s="5">
+      <c r="D59" s="21">
         <v>13</v>
       </c>
-      <c r="E59" s="5">
-        <v>31</v>
-      </c>
-      <c r="F59" s="5">
-        <v>31</v>
-      </c>
-      <c r="G59" s="9">
+      <c r="E59" s="21">
+        <v>31</v>
+      </c>
+      <c r="F59" s="21">
+        <v>31</v>
+      </c>
+      <c r="G59" s="22">
         <v>41.9354838709677</v>
       </c>
-      <c r="H59" s="9">
+      <c r="H59" s="22">
         <v>41.9354838709677</v>
       </c>
     </row>
@@ -7490,59 +7859,57 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultColWidth="11" defaultRowHeight="14.25" outlineLevelRow="6" outlineLevelCol="2"/>
+  <sheetFormatPr defaultColWidth="28.6814159292035" defaultRowHeight="15.35" outlineLevelRow="6" outlineLevelCol="2"/>
   <cols>
-    <col min="1" max="1" width="35.7079646017699" customWidth="1"/>
-    <col min="2" max="2" width="20.7079646017699" customWidth="1"/>
-    <col min="3" max="3" width="28.7079646017699" customWidth="1"/>
+    <col min="1" max="16384" width="28.6814159292035" style="13" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="18" spans="1:1">
-      <c r="A1" s="1" t="s">
+    <row r="1" ht="15" spans="1:1">
+      <c r="A1" s="19" t="s">
         <v>288</v>
       </c>
     </row>
-    <row r="4" spans="1:3">
-      <c r="A4" s="2" t="s">
+    <row r="4" ht="30" spans="1:3">
+      <c r="A4" s="7" t="s">
         <v>289</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="B4" s="7" t="s">
         <v>290</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="C4" s="7" t="s">
         <v>291</v>
       </c>
     </row>
-    <row r="5" spans="1:3">
-      <c r="A5" s="3" t="s">
+    <row r="5" ht="15.4" spans="1:3">
+      <c r="A5" s="14" t="s">
         <v>292</v>
       </c>
-      <c r="B5" s="6">
+      <c r="B5" s="16">
         <v>26</v>
       </c>
-      <c r="C5" s="6">
+      <c r="C5" s="16">
         <v>27</v>
       </c>
     </row>
-    <row r="6" spans="1:3">
-      <c r="A6" s="3" t="s">
+    <row r="6" ht="15.4" spans="1:3">
+      <c r="A6" s="14" t="s">
         <v>293</v>
       </c>
-      <c r="B6" s="6">
+      <c r="B6" s="16">
         <v>9</v>
       </c>
-      <c r="C6" s="6">
+      <c r="C6" s="16">
         <v>9</v>
       </c>
     </row>
-    <row r="7" spans="1:3">
-      <c r="A7" s="3" t="s">
+    <row r="7" ht="15.4" spans="1:3">
+      <c r="A7" s="14" t="s">
         <v>294</v>
       </c>
-      <c r="B7" s="6">
+      <c r="B7" s="16">
         <v>12</v>
       </c>
-      <c r="C7" s="6">
+      <c r="C7" s="16">
         <v>12</v>
       </c>
     </row>
